--- a/5.5.13 Real Property-Monthly Reviews-2_results.xlsx
+++ b/5.5.13 Real Property-Monthly Reviews-2_results.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.14</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -570,43 +570,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>19.6</v>
       </c>
       <c r="F2" t="n">
-        <v>55.67</v>
+        <v>105.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1436.28</v>
+        <v>28924.26</v>
       </c>
       <c r="H2" t="n">
-        <v>247.94</v>
+        <v>16728.64</v>
       </c>
       <c r="I2" t="n">
-        <v>104.44</v>
+        <v>24395.45</v>
       </c>
       <c r="J2" t="n">
-        <v>400.58</v>
+        <v>10682.1</v>
       </c>
       <c r="K2" t="n">
-        <v>403.6</v>
+        <v>27274.05</v>
       </c>
       <c r="L2" t="n">
-        <v>675.17</v>
+        <v>1608681.15</v>
       </c>
       <c r="M2" t="n">
-        <v>30.07</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>91.56999999999999</v>
+        <v>28903.7</v>
       </c>
       <c r="O2" t="n">
-        <v>67.52</v>
+        <v>16415.11</v>
       </c>
     </row>
     <row r="3">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -672,43 +672,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>496</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>496</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="G4" t="n">
-        <v>9.039999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="H4" t="n">
-        <v>7.55</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>8.029999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="J4" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>8.82</v>
+        <v>9.34</v>
       </c>
       <c r="L4" t="n">
-        <v>520.1799999999999</v>
+        <v>12164872.29</v>
       </c>
       <c r="M4" t="n">
-        <v>6.21</v>
+        <v>5.71</v>
       </c>
       <c r="N4" t="n">
-        <v>54.33</v>
+        <v>21931.43</v>
       </c>
       <c r="O4" t="n">
-        <v>28.9</v>
+        <v>12238.3</v>
       </c>
     </row>
     <row r="5">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>496</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>496</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -774,43 +774,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>4.29</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>6.57</v>
+        <v>6.71</v>
       </c>
       <c r="H6" t="n">
-        <v>5.35</v>
+        <v>5.46</v>
       </c>
       <c r="I6" t="n">
-        <v>5.21</v>
+        <v>5.49</v>
       </c>
       <c r="J6" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="K6" t="n">
-        <v>6.35</v>
+        <v>6.58</v>
       </c>
       <c r="L6" t="n">
-        <v>1894.43</v>
+        <v>2459394.43</v>
       </c>
       <c r="M6" t="n">
-        <v>26.5</v>
+        <v>72.83</v>
       </c>
       <c r="N6" t="n">
-        <v>1150.06</v>
+        <v>25765.28</v>
       </c>
       <c r="O6" t="n">
-        <v>111.44</v>
+        <v>16287.38</v>
       </c>
     </row>
     <row r="7">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -852,16 +852,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="8">
@@ -876,43 +876,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>119.85</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>139.34</v>
+        <v>163.89</v>
       </c>
       <c r="H8" t="n">
-        <v>129.59</v>
+        <v>136.72</v>
       </c>
       <c r="I8" t="n">
-        <v>139.34</v>
+        <v>144.18</v>
       </c>
       <c r="J8" t="n">
-        <v>9.75</v>
+        <v>22.68</v>
       </c>
       <c r="K8" t="n">
-        <v>137.39</v>
+        <v>159.92</v>
       </c>
       <c r="L8" t="n">
-        <v>82.8</v>
+        <v>658534.83</v>
       </c>
       <c r="M8" t="n">
-        <v>41.4</v>
+        <v>1554.84</v>
       </c>
       <c r="N8" t="n">
-        <v>41.4</v>
+        <v>25643.27</v>
       </c>
       <c r="O8" t="n">
-        <v>41.4</v>
+        <v>14315.97</v>
       </c>
     </row>
     <row r="9">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -978,43 +978,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>9.42</v>
+        <v>6.68</v>
       </c>
       <c r="G10" t="n">
-        <v>10.1</v>
+        <v>12.03</v>
       </c>
       <c r="H10" t="n">
-        <v>9.76</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.34</v>
+        <v>1.59</v>
       </c>
       <c r="K10" t="n">
-        <v>10.03</v>
+        <v>11.81</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1166.69</v>
       </c>
       <c r="M10" t="n">
-        <v>1.49</v>
+        <v>0.84</v>
       </c>
       <c r="N10" t="n">
-        <v>1.49</v>
+        <v>1081.49</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>55.56</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,20 +1070,20 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45662.29166666666</v>
+        <v>45662.29305555556</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45662.33032439081</v>
+        <v>45662.36645138443</v>
       </c>
       <c r="D2" t="n">
-        <v>55.67</v>
+        <v>105.69</v>
       </c>
       <c r="E2" t="n">
-        <v>30.07</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45662.29305555556</v>
+        <v>45662.29444444444</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45662.35642806848</v>
+        <v>45662.38976335743</v>
       </c>
       <c r="D3" t="n">
-        <v>91.26000000000001</v>
+        <v>137.26</v>
       </c>
       <c r="E3" t="n">
-        <v>66.63</v>
+        <v>110.29</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45662.29583333333</v>
+        <v>45662.29861111111</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45662.35960907352</v>
+        <v>45662.42868614953</v>
       </c>
       <c r="D4" t="n">
-        <v>91.84</v>
+        <v>187.31</v>
       </c>
       <c r="E4" t="n">
-        <v>69.87</v>
+        <v>163.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45662.29444444444</v>
+        <v>45662.29722222222</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45662.36259056679</v>
+        <v>45662.44845628603</v>
       </c>
       <c r="D5" t="n">
-        <v>98.13</v>
+        <v>217.78</v>
       </c>
       <c r="E5" t="n">
-        <v>72.23</v>
+        <v>190.43</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45662.29722222222</v>
+        <v>45662.30138888889</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45662.36676671969</v>
+        <v>45662.48071878951</v>
       </c>
       <c r="D6" t="n">
-        <v>100.14</v>
+        <v>258.24</v>
       </c>
       <c r="E6" t="n">
-        <v>72.04000000000001</v>
+        <v>232.47</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45662.29861111111</v>
+        <v>45662.3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>45662.37114121031</v>
+        <v>45662.5065587278</v>
       </c>
       <c r="D7" t="n">
-        <v>104.44</v>
+        <v>297.44</v>
       </c>
       <c r="E7" t="n">
-        <v>76.12</v>
+        <v>266.76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45662.30138888889</v>
+        <v>45662.30277777778</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45662.37475641909</v>
+        <v>45662.53846813237</v>
       </c>
       <c r="D8" t="n">
-        <v>105.65</v>
+        <v>339.39</v>
       </c>
       <c r="E8" t="n">
-        <v>79.90000000000001</v>
+        <v>312.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>45662.30416666667</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45662.37855292698</v>
+        <v>45663.31160759155</v>
       </c>
       <c r="D9" t="n">
-        <v>107.12</v>
+        <v>1450.71</v>
       </c>
       <c r="E9" t="n">
-        <v>80.83</v>
+        <v>1424.26</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1262,20 +1262,20 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45662.3</v>
+        <v>45662.30555555555</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45662.50059628971</v>
+        <v>45663.35538182678</v>
       </c>
       <c r="D10" t="n">
-        <v>288.86</v>
+        <v>1511.75</v>
       </c>
       <c r="E10" t="n">
-        <v>35.91</v>
+        <v>1484.22</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1286,20 +1286,2132 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45662.30277777778</v>
+        <v>45662.30972222222</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>45663.30019608489</v>
+        <v>45663.42082936655</v>
       </c>
       <c r="D11" t="n">
-        <v>1436.28</v>
+        <v>1599.99</v>
       </c>
       <c r="E11" t="n">
-        <v>91.56999999999999</v>
+        <v>1572.94</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45662.31111111111</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45663.43756760391</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1622.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1593.55</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45662.3125</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>45663.45847163483</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1650.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1626.5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45662.29166666666</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>45664.30815304205</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2903.74</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1560.55</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45662.31388888889</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>45664.32437194397</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2895.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2866.72</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45662.31666666667</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>45664.36708358242</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2952.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2926.07</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45662.31805555556</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>45664.3911052832</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2985.19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2957.56</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45662.31944444445</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>45664.41210877281</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3013.44</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2990.26</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45662.29583333333</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>45664.52086205893</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3204.04</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2903.83</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45662.30694444444</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>45665.38403227897</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4431.01</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4193.1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45662.32361111111</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>45665.40692868298</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4439.98</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4409.59</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45662.325</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>45665.43328906162</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4475.94</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4448.8</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45662.32638888889</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>45665.46620902592</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4521.34</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4493.77</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45662.32777777778</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>45666.29429208017</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5711.78</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5682.46</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45662.30833333333</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>45666.3040366191</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5753.81</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4449.12</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45662.32916666667</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>45666.31231671977</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5735.74</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5711.17</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45662.33055555556</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>45666.3440128232</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5779.38</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5751.91</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45662.33472222222</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>45666.42224247838</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5886.03</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5858.69</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45662.3375</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>45666.44357719753</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5912.75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5887.26</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45662.33611111111</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>45666.48088651554</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5968.48</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5939.26</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45662.31527777778</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>45667.30684073463</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7187.85</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5865.73</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45662.32222222222</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>45667.40033280636</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7312.48</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7040.8</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45662.34027777778</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>45667.41567139886</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7308.57</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7280.98</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45662.32083333333</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>45667.53905372047</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7514.24</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7189.18</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45662.34166666667</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>45668.37213282687</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8683.870000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8652.77</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45662.5125</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>45668.37665576444</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8444.379999999999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7223.66</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45662.33333333334</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>45669.29813801696</v>
+      </c>
+      <c r="D37" t="n">
+        <v>10029.32</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8700.139999999999</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45662.33194444444</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>45669.44341529907</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10240.52</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8867.91</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45662.33888888889</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>45670.29917730377</v>
+      </c>
+      <c r="D39" t="n">
+        <v>11462.82</v>
+      </c>
+      <c r="E39" t="n">
+        <v>10140.18</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45662.34305555555</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>45670.30530554261</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11465.64</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9241.959999999999</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45662.34444444445</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>45670.39254016999</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11589.26</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10333.17</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45662.34583333333</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>45670.49629648884</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11736.67</v>
+      </c>
+      <c r="E42" t="n">
+        <v>10466.77</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45662.67638888889</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>45671.40506611325</v>
+      </c>
+      <c r="D43" t="n">
+        <v>12569.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10412.57</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45662.34722222222</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>45671.4442688503</v>
+      </c>
+      <c r="D44" t="n">
+        <v>13099.75</v>
+      </c>
+      <c r="E44" t="n">
+        <v>11994.14</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45662.65416666667</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>45672.41320499728</v>
+      </c>
+      <c r="D45" t="n">
+        <v>14053.02</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11856.79</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45662.83611111111</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>45673.39680912522</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15207.41</v>
+      </c>
+      <c r="E46" t="n">
+        <v>13206.89</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45662.34861111111</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>45678.53756186798</v>
+      </c>
+      <c r="D47" t="n">
+        <v>23312.09</v>
+      </c>
+      <c r="E47" t="n">
+        <v>23285.71</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45662.35138888889</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>45678.54159214268</v>
+      </c>
+      <c r="D48" t="n">
+        <v>23313.89</v>
+      </c>
+      <c r="E48" t="n">
+        <v>23289.18</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45662.35277777778</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>45679.29166666666</v>
+      </c>
+      <c r="D49" t="n">
+        <v>24392</v>
+      </c>
+      <c r="E49" t="n">
+        <v>23286.55</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45662.35555555556</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>45679.29528940734</v>
+      </c>
+      <c r="D50" t="n">
+        <v>24393.22</v>
+      </c>
+      <c r="E50" t="n">
+        <v>24363.93</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45662.35694444444</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>45679.29823183955</v>
+      </c>
+      <c r="D51" t="n">
+        <v>24395.45</v>
+      </c>
+      <c r="E51" t="n">
+        <v>24368.49</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45662.35833333333</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>45679.30286373736</v>
+      </c>
+      <c r="D52" t="n">
+        <v>24400.12</v>
+      </c>
+      <c r="E52" t="n">
+        <v>24371.5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45662.35972222222</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>45679.30733133603</v>
+      </c>
+      <c r="D53" t="n">
+        <v>24404.56</v>
+      </c>
+      <c r="E53" t="n">
+        <v>24375.82</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45662.3625</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>45679.31113674448</v>
+      </c>
+      <c r="D54" t="n">
+        <v>24406.04</v>
+      </c>
+      <c r="E54" t="n">
+        <v>24377.02</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45662.36388888889</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>45679.3156680484</v>
+      </c>
+      <c r="D55" t="n">
+        <v>24410.56</v>
+      </c>
+      <c r="E55" t="n">
+        <v>24381.76</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45662.36666666667</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>45679.39527230465</v>
+      </c>
+      <c r="D56" t="n">
+        <v>24521.19</v>
+      </c>
+      <c r="E56" t="n">
+        <v>24498.06</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>45662.36805555555</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>45679.39808909513</v>
+      </c>
+      <c r="D57" t="n">
+        <v>24523.25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>24497.84</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>45662.36944444444</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>45679.40209335557</v>
+      </c>
+      <c r="D58" t="n">
+        <v>24527.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>24499.49</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>45662.35416666666</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>45679.40457191706</v>
+      </c>
+      <c r="D59" t="n">
+        <v>24552.58</v>
+      </c>
+      <c r="E59" t="n">
+        <v>24334.01</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>45662.37222222222</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>45679.4054014357</v>
+      </c>
+      <c r="D60" t="n">
+        <v>24527.78</v>
+      </c>
+      <c r="E60" t="n">
+        <v>24504.72</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>45662.37083333333</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>45679.47772115074</v>
+      </c>
+      <c r="D61" t="n">
+        <v>24633.92</v>
+      </c>
+      <c r="E61" t="n">
+        <v>24606.84</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>45662.37361111111</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>45679.48015942366</v>
+      </c>
+      <c r="D62" t="n">
+        <v>24633.43</v>
+      </c>
+      <c r="E62" t="n">
+        <v>24609.86</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>45662.37638888889</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>45679.4842906786</v>
+      </c>
+      <c r="D63" t="n">
+        <v>24635.38</v>
+      </c>
+      <c r="E63" t="n">
+        <v>24608.39</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>45662.35</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>45679.48824747477</v>
+      </c>
+      <c r="D64" t="n">
+        <v>24679.08</v>
+      </c>
+      <c r="E64" t="n">
+        <v>24407.38</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>45662.37777777778</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>45679.48845420307</v>
+      </c>
+      <c r="D65" t="n">
+        <v>24639.37</v>
+      </c>
+      <c r="E65" t="n">
+        <v>24608.73</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>45662.37916666667</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>45679.4929093571</v>
+      </c>
+      <c r="D66" t="n">
+        <v>24643.79</v>
+      </c>
+      <c r="E66" t="n">
+        <v>24613.99</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>45662.38333333333</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>45679.49740435466</v>
+      </c>
+      <c r="D67" t="n">
+        <v>24644.26</v>
+      </c>
+      <c r="E67" t="n">
+        <v>24616.11</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>45662.38194444445</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>45679.50081486114</v>
+      </c>
+      <c r="D68" t="n">
+        <v>24651.17</v>
+      </c>
+      <c r="E68" t="n">
+        <v>24624.37</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>45662.36111111111</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>45680.30615307333</v>
+      </c>
+      <c r="D69" t="n">
+        <v>25840.86</v>
+      </c>
+      <c r="E69" t="n">
+        <v>24520</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>45662.38472222222</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>45680.40084635137</v>
+      </c>
+      <c r="D70" t="n">
+        <v>25943.22</v>
+      </c>
+      <c r="E70" t="n">
+        <v>25912.95</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>45662.38611111111</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>45680.40517113198</v>
+      </c>
+      <c r="D71" t="n">
+        <v>25947.45</v>
+      </c>
+      <c r="E71" t="n">
+        <v>25921.01</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>45662.36527777778</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>45680.40836026006</v>
+      </c>
+      <c r="D72" t="n">
+        <v>25982.04</v>
+      </c>
+      <c r="E72" t="n">
+        <v>25666.25</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>45662.3875</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>45680.40967682941</v>
+      </c>
+      <c r="D73" t="n">
+        <v>25951.93</v>
+      </c>
+      <c r="E73" t="n">
+        <v>25924.95</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>45662.38055555556</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>45680.5357645696</v>
+      </c>
+      <c r="D74" t="n">
+        <v>26143.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>25832.45</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>45662.375</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>45681.29936357489</v>
+      </c>
+      <c r="D75" t="n">
+        <v>27251.08</v>
+      </c>
+      <c r="E75" t="n">
+        <v>25950.42</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>45662.38888888889</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>45681.3021171319</v>
+      </c>
+      <c r="D76" t="n">
+        <v>27235.05</v>
+      </c>
+      <c r="E76" t="n">
+        <v>27208.32</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>45662.39027777778</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>45681.30630891504</v>
+      </c>
+      <c r="D77" t="n">
+        <v>27239.08</v>
+      </c>
+      <c r="E77" t="n">
+        <v>27211.24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>45662.39166666667</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>45681.30929125974</v>
+      </c>
+      <c r="D78" t="n">
+        <v>27241.38</v>
+      </c>
+      <c r="E78" t="n">
+        <v>27213.53</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>45662.39305555556</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>45681.31366135218</v>
+      </c>
+      <c r="D79" t="n">
+        <v>27245.67</v>
+      </c>
+      <c r="E79" t="n">
+        <v>27217.19</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>45662.39444444444</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>45681.31803175672</v>
+      </c>
+      <c r="D80" t="n">
+        <v>27249.97</v>
+      </c>
+      <c r="E80" t="n">
+        <v>27222.06</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>45662.39722222222</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>45681.3209855744</v>
+      </c>
+      <c r="D81" t="n">
+        <v>27250.22</v>
+      </c>
+      <c r="E81" t="n">
+        <v>27225.54</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>45662.39861111111</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>45681.3242839368</v>
+      </c>
+      <c r="D82" t="n">
+        <v>27252.97</v>
+      </c>
+      <c r="E82" t="n">
+        <v>27226.11</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>45662.4</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>45681.32760307437</v>
+      </c>
+      <c r="D83" t="n">
+        <v>27255.75</v>
+      </c>
+      <c r="E83" t="n">
+        <v>27231.83</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>45662.40277777778</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>45681.33119633021</v>
+      </c>
+      <c r="D84" t="n">
+        <v>27256.92</v>
+      </c>
+      <c r="E84" t="n">
+        <v>27228.59</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>45662.40555555555</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>45681.33461168112</v>
+      </c>
+      <c r="D85" t="n">
+        <v>27257.84</v>
+      </c>
+      <c r="E85" t="n">
+        <v>27235.5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>45662.40416666667</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>45681.33846355641</v>
+      </c>
+      <c r="D86" t="n">
+        <v>27265.39</v>
+      </c>
+      <c r="E86" t="n">
+        <v>27234.89</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>45662.40694444445</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>45681.34197540774</v>
+      </c>
+      <c r="D87" t="n">
+        <v>27266.44</v>
+      </c>
+      <c r="E87" t="n">
+        <v>27237.76</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>45662.40833333333</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>45681.34628781332</v>
+      </c>
+      <c r="D88" t="n">
+        <v>27270.65</v>
+      </c>
+      <c r="E88" t="n">
+        <v>27242.27</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>45662.40972222222</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>45681.34972006597</v>
+      </c>
+      <c r="D89" t="n">
+        <v>27273.6</v>
+      </c>
+      <c r="E89" t="n">
+        <v>27244.35</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>45662.4125</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>45681.35353542436</v>
+      </c>
+      <c r="D90" t="n">
+        <v>27275.09</v>
+      </c>
+      <c r="E90" t="n">
+        <v>27248.95</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>45662.41388888889</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>45681.35595963308</v>
+      </c>
+      <c r="D91" t="n">
+        <v>27276.58</v>
+      </c>
+      <c r="E91" t="n">
+        <v>27248.41</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>45662.41527777778</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>45681.36052819547</v>
+      </c>
+      <c r="D92" t="n">
+        <v>27281.16</v>
+      </c>
+      <c r="E92" t="n">
+        <v>27254.37</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>45662.41111111111</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>45682.4118632898</v>
+      </c>
+      <c r="D93" t="n">
+        <v>28801.08</v>
+      </c>
+      <c r="E93" t="n">
+        <v>28502.08</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>45662.41666666666</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>45682.41508173538</v>
+      </c>
+      <c r="D94" t="n">
+        <v>28797.72</v>
+      </c>
+      <c r="E94" t="n">
+        <v>28772.41</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>45662.41805555556</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>45682.41875947017</v>
+      </c>
+      <c r="D95" t="n">
+        <v>28801.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>28775.32</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>45662.41944444444</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>45682.42328160448</v>
+      </c>
+      <c r="D96" t="n">
+        <v>28805.53</v>
+      </c>
+      <c r="E96" t="n">
+        <v>28777.75</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>45662.42361111111</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>45682.42780392143</v>
+      </c>
+      <c r="D97" t="n">
+        <v>28806.04</v>
+      </c>
+      <c r="E97" t="n">
+        <v>28781.2</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>45662.42222222222</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>45682.50846915448</v>
+      </c>
+      <c r="D98" t="n">
+        <v>28924.2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>27819.88</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>45662.425</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>45682.511289335</v>
+      </c>
+      <c r="D99" t="n">
+        <v>28924.26</v>
+      </c>
+      <c r="E99" t="n">
+        <v>28903.7</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1336,7 +3448,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -1346,7 +3458,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
@@ -1356,7 +3468,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1366,7 +3478,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.76</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1376,7 +3488,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.03</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="7">
@@ -1386,7 +3498,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.49</v>
+        <v>55.56</v>
       </c>
     </row>
   </sheetData>

--- a/5.5.13 Real Property-Monthly Reviews-2_results.xlsx
+++ b/5.5.13 Real Property-Monthly Reviews-2_results.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.79</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -573,40 +573,40 @@
         <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
-        <v>19.6</v>
+        <v>24.8</v>
       </c>
       <c r="F2" t="n">
-        <v>105.69</v>
+        <v>59.95</v>
       </c>
       <c r="G2" t="n">
-        <v>28924.26</v>
+        <v>31612.33</v>
       </c>
       <c r="H2" t="n">
-        <v>16728.64</v>
+        <v>18879.43</v>
       </c>
       <c r="I2" t="n">
-        <v>24395.45</v>
+        <v>23077.82</v>
       </c>
       <c r="J2" t="n">
-        <v>10682.1</v>
+        <v>10449.24</v>
       </c>
       <c r="K2" t="n">
-        <v>27274.05</v>
+        <v>30030.93</v>
       </c>
       <c r="L2" t="n">
-        <v>1608681.15</v>
+        <v>2304145.7</v>
       </c>
       <c r="M2" t="n">
-        <v>78.54000000000001</v>
+        <v>32.97</v>
       </c>
       <c r="N2" t="n">
-        <v>28903.7</v>
+        <v>31276.63</v>
       </c>
       <c r="O2" t="n">
-        <v>16415.11</v>
+        <v>18581.82</v>
       </c>
     </row>
     <row r="3">
@@ -672,43 +672,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D4" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>5.12</v>
+        <v>5.19</v>
       </c>
       <c r="G4" t="n">
         <v>9.58</v>
       </c>
       <c r="H4" t="n">
-        <v>8.029999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I4" t="n">
-        <v>8.18</v>
+        <v>8.24</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
-        <v>9.34</v>
+        <v>9.35</v>
       </c>
       <c r="L4" t="n">
-        <v>12164872.29</v>
+        <v>10183752.51</v>
       </c>
       <c r="M4" t="n">
-        <v>5.71</v>
+        <v>6.21</v>
       </c>
       <c r="N4" t="n">
-        <v>21931.43</v>
+        <v>20332.4</v>
       </c>
       <c r="O4" t="n">
-        <v>12238.3</v>
+        <v>10255.54</v>
       </c>
     </row>
     <row r="5">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D5" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -774,43 +774,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="G6" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
       <c r="H6" t="n">
-        <v>5.46</v>
+        <v>5.53</v>
       </c>
       <c r="I6" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="J6" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="K6" t="n">
-        <v>6.58</v>
+        <v>6.55</v>
       </c>
       <c r="L6" t="n">
-        <v>2459394.43</v>
+        <v>3098701.11</v>
       </c>
       <c r="M6" t="n">
-        <v>72.83</v>
+        <v>32.97</v>
       </c>
       <c r="N6" t="n">
-        <v>25765.28</v>
+        <v>27225.48</v>
       </c>
       <c r="O6" t="n">
-        <v>16287.38</v>
+        <v>16570.59</v>
       </c>
     </row>
     <row r="7">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -852,16 +852,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9.32</v>
+        <v>8.57</v>
       </c>
       <c r="M7" t="n">
-        <v>9.32</v>
+        <v>8.57</v>
       </c>
       <c r="N7" t="n">
-        <v>9.32</v>
+        <v>8.57</v>
       </c>
       <c r="O7" t="n">
-        <v>9.32</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="8">
@@ -876,43 +876,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>77.70999999999999</v>
+        <v>70.27</v>
       </c>
       <c r="G8" t="n">
-        <v>163.89</v>
+        <v>161.49</v>
       </c>
       <c r="H8" t="n">
-        <v>136.72</v>
+        <v>126.06</v>
       </c>
       <c r="I8" t="n">
-        <v>144.18</v>
+        <v>133.75</v>
       </c>
       <c r="J8" t="n">
-        <v>22.68</v>
+        <v>27.1</v>
       </c>
       <c r="K8" t="n">
-        <v>159.92</v>
+        <v>156.43</v>
       </c>
       <c r="L8" t="n">
-        <v>658534.83</v>
+        <v>1031770.38</v>
       </c>
       <c r="M8" t="n">
-        <v>1554.84</v>
+        <v>1510.3</v>
       </c>
       <c r="N8" t="n">
-        <v>25643.27</v>
+        <v>27125.38</v>
       </c>
       <c r="O8" t="n">
-        <v>14315.97</v>
+        <v>19106.86</v>
       </c>
     </row>
     <row r="9">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -978,43 +978,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>95.65000000000001</v>
+        <v>96.77</v>
       </c>
       <c r="F10" t="n">
-        <v>6.68</v>
+        <v>7.59</v>
       </c>
       <c r="G10" t="n">
-        <v>12.03</v>
+        <v>12.07</v>
       </c>
       <c r="H10" t="n">
-        <v>9.710000000000001</v>
+        <v>10.36</v>
       </c>
       <c r="I10" t="n">
-        <v>9.5</v>
+        <v>10.58</v>
       </c>
       <c r="J10" t="n">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="K10" t="n">
-        <v>11.81</v>
+        <v>11.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1166.69</v>
+        <v>129.44</v>
       </c>
       <c r="M10" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1081.49</v>
+        <v>6.83</v>
       </c>
       <c r="O10" t="n">
-        <v>55.56</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,20 +1070,20 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45662.29305555556</v>
+        <v>45662.29166666666</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45662.36645138443</v>
+        <v>45662.33329752198</v>
       </c>
       <c r="D2" t="n">
-        <v>105.69</v>
+        <v>59.95</v>
       </c>
       <c r="E2" t="n">
-        <v>78.54000000000001</v>
+        <v>32.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45662.29444444444</v>
+        <v>45662.29305555556</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45662.38976335743</v>
+        <v>45662.37334402597</v>
       </c>
       <c r="D3" t="n">
-        <v>137.26</v>
+        <v>115.62</v>
       </c>
       <c r="E3" t="n">
-        <v>110.29</v>
+        <v>87.23</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45662.29861111111</v>
+        <v>45662.29583333333</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45662.42868614953</v>
+        <v>45662.40163947275</v>
       </c>
       <c r="D4" t="n">
-        <v>187.31</v>
+        <v>152.36</v>
       </c>
       <c r="E4" t="n">
-        <v>163.52</v>
+        <v>125.87</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1145,13 +1145,13 @@
         <v>45662.29722222222</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45662.44845628603</v>
+        <v>45662.43762263396</v>
       </c>
       <c r="D5" t="n">
-        <v>217.78</v>
+        <v>202.18</v>
       </c>
       <c r="E5" t="n">
-        <v>190.43</v>
+        <v>179.17</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45662.30138888889</v>
+        <v>45662.29861111111</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45662.48071878951</v>
+        <v>45662.46990041722</v>
       </c>
       <c r="D6" t="n">
-        <v>258.24</v>
+        <v>246.66</v>
       </c>
       <c r="E6" t="n">
-        <v>232.47</v>
+        <v>219.67</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,13 +1193,13 @@
         <v>45662.3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>45662.5065587278</v>
+        <v>45662.51885033459</v>
       </c>
       <c r="D7" t="n">
-        <v>297.44</v>
+        <v>315.14</v>
       </c>
       <c r="E7" t="n">
-        <v>266.76</v>
+        <v>285.13</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45662.30277777778</v>
+        <v>45662.30138888889</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45662.53846813237</v>
+        <v>45662.5399183164</v>
       </c>
       <c r="D8" t="n">
-        <v>339.39</v>
+        <v>343.48</v>
       </c>
       <c r="E8" t="n">
-        <v>312.8</v>
+        <v>316.25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45662.30416666667</v>
+        <v>45662.30277777778</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45663.31160759155</v>
+        <v>45663.31580679751</v>
       </c>
       <c r="D9" t="n">
-        <v>1450.71</v>
+        <v>1458.76</v>
       </c>
       <c r="E9" t="n">
-        <v>1424.26</v>
+        <v>1431.38</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45662.30555555555</v>
+        <v>45662.30416666667</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45663.35538182678</v>
+        <v>45663.35101653879</v>
       </c>
       <c r="D10" t="n">
-        <v>1511.75</v>
+        <v>1507.46</v>
       </c>
       <c r="E10" t="n">
-        <v>1484.22</v>
+        <v>1480.52</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45662.30972222222</v>
+        <v>45662.30555555555</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>45663.42082936655</v>
+        <v>45663.39079347986</v>
       </c>
       <c r="D11" t="n">
-        <v>1599.99</v>
+        <v>1562.74</v>
       </c>
       <c r="E11" t="n">
-        <v>1572.94</v>
+        <v>1532.57</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45662.31111111111</v>
+        <v>45662.30833333333</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45663.43756760391</v>
+        <v>45663.43154756449</v>
       </c>
       <c r="D12" t="n">
-        <v>1622.1</v>
+        <v>1617.43</v>
       </c>
       <c r="E12" t="n">
-        <v>1593.55</v>
+        <v>1589.82</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1334,20 +1334,20 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45662.3125</v>
+        <v>45662.29444444444</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>45663.45847163483</v>
+        <v>45663.5338707749</v>
       </c>
       <c r="D13" t="n">
-        <v>1650.2</v>
+        <v>1784.77</v>
       </c>
       <c r="E13" t="n">
-        <v>1626.5</v>
+        <v>1532.25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1358,20 +1358,20 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45662.29166666666</v>
+        <v>45662.31111111111</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>45664.30815304205</v>
+        <v>45664.3203193547</v>
       </c>
       <c r="D14" t="n">
-        <v>2903.74</v>
+        <v>2893.26</v>
       </c>
       <c r="E14" t="n">
-        <v>1560.55</v>
+        <v>2864.74</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1382,16 +1382,16 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45662.31388888889</v>
+        <v>45662.3125</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>45664.32437194397</v>
+        <v>45664.34962421956</v>
       </c>
       <c r="D15" t="n">
-        <v>2895.1</v>
+        <v>2933.46</v>
       </c>
       <c r="E15" t="n">
-        <v>2866.72</v>
+        <v>2907.38</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45662.31666666667</v>
+        <v>45662.31527777778</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>45664.36708358242</v>
+        <v>45664.41355094349</v>
       </c>
       <c r="D16" t="n">
-        <v>2952.6</v>
+        <v>3021.51</v>
       </c>
       <c r="E16" t="n">
-        <v>2926.07</v>
+        <v>2990.55</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45662.31805555556</v>
+        <v>45662.31666666667</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>45664.3911052832</v>
+        <v>45664.43969734229</v>
       </c>
       <c r="D17" t="n">
-        <v>2985.19</v>
+        <v>3057.16</v>
       </c>
       <c r="E17" t="n">
-        <v>2957.56</v>
+        <v>3029.78</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1454,16 +1454,16 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45662.31944444445</v>
+        <v>45662.31805555556</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>45664.41210877281</v>
+        <v>45664.46696351265</v>
       </c>
       <c r="D18" t="n">
-        <v>3013.44</v>
+        <v>3094.43</v>
       </c>
       <c r="E18" t="n">
-        <v>2990.26</v>
+        <v>3065.71</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1478,20 +1478,20 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45662.29583333333</v>
+        <v>45662.32222222222</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>45664.52086205893</v>
+        <v>45665.30706725767</v>
       </c>
       <c r="D19" t="n">
-        <v>3204.04</v>
+        <v>4298.18</v>
       </c>
       <c r="E19" t="n">
-        <v>2903.83</v>
+        <v>4270.89</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1502,20 +1502,20 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45662.30694444444</v>
+        <v>45662.32361111111</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>45665.38403227897</v>
+        <v>45665.33880627694</v>
       </c>
       <c r="D20" t="n">
-        <v>4431.01</v>
+        <v>4341.88</v>
       </c>
       <c r="E20" t="n">
-        <v>4193.1</v>
+        <v>4312.75</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45662.32361111111</v>
+        <v>45662.325</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>45665.40692868298</v>
+        <v>45665.36845109234</v>
       </c>
       <c r="D21" t="n">
-        <v>4439.98</v>
+        <v>4382.57</v>
       </c>
       <c r="E21" t="n">
-        <v>4409.59</v>
+        <v>4353.12</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1550,20 +1550,20 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45662.325</v>
+        <v>45662.31388888889</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45665.43328906162</v>
+        <v>45665.49950817604</v>
       </c>
       <c r="D22" t="n">
-        <v>4475.94</v>
+        <v>4587.29</v>
       </c>
       <c r="E22" t="n">
-        <v>4448.8</v>
+        <v>4318.61</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1574,20 +1574,20 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45662.32638888889</v>
+        <v>45662.30694444444</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>45665.46620902592</v>
+        <v>45666.30669177544</v>
       </c>
       <c r="D23" t="n">
-        <v>4521.34</v>
+        <v>5759.64</v>
       </c>
       <c r="E23" t="n">
-        <v>4493.77</v>
+        <v>4419.3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1601,13 +1601,13 @@
         <v>45662.32777777778</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>45666.29429208017</v>
+        <v>45666.31027586611</v>
       </c>
       <c r="D24" t="n">
-        <v>5711.78</v>
+        <v>5734.8</v>
       </c>
       <c r="E24" t="n">
-        <v>5682.46</v>
+        <v>5711.16</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1622,20 +1622,20 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45662.30833333333</v>
+        <v>45662.32638888889</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>45666.3040366191</v>
+        <v>45666.33877452159</v>
       </c>
       <c r="D25" t="n">
-        <v>5753.81</v>
+        <v>5777.84</v>
       </c>
       <c r="E25" t="n">
-        <v>4449.12</v>
+        <v>5749.81</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1649,13 @@
         <v>45662.32916666667</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>45666.31231671977</v>
+        <v>45666.3760189571</v>
       </c>
       <c r="D26" t="n">
-        <v>5735.74</v>
+        <v>5827.47</v>
       </c>
       <c r="E26" t="n">
-        <v>5711.17</v>
+        <v>5797.79</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45662.33055555556</v>
+        <v>45662.33194444444</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45666.3440128232</v>
+        <v>45666.39543306366</v>
       </c>
       <c r="D27" t="n">
-        <v>5779.38</v>
+        <v>5851.42</v>
       </c>
       <c r="E27" t="n">
-        <v>5751.91</v>
+        <v>5825.24</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45662.33472222222</v>
+        <v>45662.33055555556</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>45666.42224247838</v>
+        <v>45666.4291758629</v>
       </c>
       <c r="D28" t="n">
-        <v>5886.03</v>
+        <v>5902.01</v>
       </c>
       <c r="E28" t="n">
-        <v>5858.69</v>
+        <v>5873.09</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45662.3375</v>
+        <v>45662.33333333334</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>45666.44357719753</v>
+        <v>45666.44954801867</v>
       </c>
       <c r="D29" t="n">
-        <v>5912.75</v>
+        <v>5927.35</v>
       </c>
       <c r="E29" t="n">
-        <v>5887.26</v>
+        <v>5901.38</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1742,20 +1742,20 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45662.33611111111</v>
+        <v>45662.30972222222</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45666.48088651554</v>
+        <v>45667.30633220963</v>
       </c>
       <c r="D30" t="n">
-        <v>5968.48</v>
+        <v>7195.12</v>
       </c>
       <c r="E30" t="n">
-        <v>5939.26</v>
+        <v>5796.98</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45662.31527777778</v>
+        <v>45662.48888888889</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>45667.30684073463</v>
+        <v>45667.37023438902</v>
       </c>
       <c r="D31" t="n">
-        <v>7187.85</v>
+        <v>7029.14</v>
       </c>
       <c r="E31" t="n">
-        <v>5865.73</v>
+        <v>5687.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45662.32222222222</v>
+        <v>45662.32083333333</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>45667.40033280636</v>
+        <v>45667.47586051536</v>
       </c>
       <c r="D32" t="n">
-        <v>7312.48</v>
+        <v>7423.24</v>
       </c>
       <c r="E32" t="n">
-        <v>7040.8</v>
+        <v>7158.56</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45662.34027777778</v>
+        <v>45662.33611111111</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>45667.41567139886</v>
+        <v>45667.48772982143</v>
       </c>
       <c r="D33" t="n">
-        <v>7308.57</v>
+        <v>7418.33</v>
       </c>
       <c r="E33" t="n">
-        <v>7280.98</v>
+        <v>7389.91</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1838,20 +1838,20 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45662.32083333333</v>
+        <v>45662.3375</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>45667.53905372047</v>
+        <v>45667.52647083604</v>
       </c>
       <c r="D34" t="n">
-        <v>7514.24</v>
+        <v>7472.12</v>
       </c>
       <c r="E34" t="n">
-        <v>7189.18</v>
+        <v>7444.75</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45662.34166666667</v>
+        <v>45662.34027777778</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>45668.37213282687</v>
+        <v>45668.41375448016</v>
       </c>
       <c r="D35" t="n">
-        <v>8683.870000000001</v>
+        <v>8745.809999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>8652.77</v>
+        <v>8720.639999999999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45662.5125</v>
+        <v>45662.31944444445</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>45668.37665576444</v>
+        <v>45668.41976485375</v>
       </c>
       <c r="D36" t="n">
-        <v>8444.379999999999</v>
+        <v>8784.459999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>7223.66</v>
+        <v>8457.84</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1910,20 +1910,20 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45662.33333333334</v>
+        <v>45662.33888888889</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>45669.29813801696</v>
+        <v>45668.44414685827</v>
       </c>
       <c r="D37" t="n">
-        <v>10029.32</v>
+        <v>8791.57</v>
       </c>
       <c r="E37" t="n">
-        <v>8700.139999999999</v>
+        <v>8764.33</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1934,20 +1934,20 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45662.33194444444</v>
+        <v>45662.34166666667</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>45669.44341529907</v>
+        <v>45668.4639501508</v>
       </c>
       <c r="D38" t="n">
-        <v>10240.52</v>
+        <v>8816.09</v>
       </c>
       <c r="E38" t="n">
-        <v>8867.91</v>
+        <v>8794.24</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1958,20 +1958,20 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45662.33888888889</v>
+        <v>45662.34305555555</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>45670.29917730377</v>
+        <v>45668.50091386359</v>
       </c>
       <c r="D39" t="n">
-        <v>11462.82</v>
+        <v>8867.32</v>
       </c>
       <c r="E39" t="n">
-        <v>10140.18</v>
+        <v>8841.049999999999</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45662.34305555555</v>
+        <v>45662.33472222222</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>45670.30530554261</v>
+        <v>45669.30678219995</v>
       </c>
       <c r="D40" t="n">
-        <v>11465.64</v>
+        <v>10039.77</v>
       </c>
       <c r="E40" t="n">
-        <v>9241.959999999999</v>
+        <v>7766.26</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2009,17 +2009,17 @@
         <v>45662.34444444445</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>45670.39254016999</v>
+        <v>45669.53506792918</v>
       </c>
       <c r="D41" t="n">
-        <v>11589.26</v>
+        <v>10354.5</v>
       </c>
       <c r="E41" t="n">
-        <v>10333.17</v>
+        <v>9250.26</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2030,20 +2030,20 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45662.34583333333</v>
+        <v>45662.85138888889</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>45670.49629648884</v>
+        <v>45670.41012530989</v>
       </c>
       <c r="D42" t="n">
-        <v>11736.67</v>
+        <v>10884.58</v>
       </c>
       <c r="E42" t="n">
-        <v>10466.77</v>
+        <v>8970.440000000001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45662.67638888889</v>
+        <v>45662.69305555556</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>45671.40506611325</v>
+        <v>45674.41309944067</v>
       </c>
       <c r="D43" t="n">
-        <v>12569.3</v>
+        <v>16876.86</v>
       </c>
       <c r="E43" t="n">
-        <v>10412.57</v>
+        <v>14727.07</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45662.34722222222</v>
+        <v>45662.88472222222</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>45671.4442688503</v>
+        <v>45675.41094876696</v>
       </c>
       <c r="D44" t="n">
-        <v>13099.75</v>
+        <v>18037.77</v>
       </c>
       <c r="E44" t="n">
-        <v>11994.14</v>
+        <v>16140.3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2102,20 +2102,20 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45662.65416666667</v>
+        <v>45662.83333333334</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>45672.41320499728</v>
+        <v>45677.36096354036</v>
       </c>
       <c r="D45" t="n">
-        <v>14053.02</v>
+        <v>20919.79</v>
       </c>
       <c r="E45" t="n">
-        <v>11856.79</v>
+        <v>19061.21</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2126,20 +2126,20 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45662.83611111111</v>
+        <v>45662.34722222222</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>45673.39680912522</v>
+        <v>45677.42750575664</v>
       </c>
       <c r="D46" t="n">
-        <v>15207.41</v>
+        <v>21715.61</v>
       </c>
       <c r="E46" t="n">
-        <v>13206.89</v>
+        <v>21688.09</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2153,13 +2153,13 @@
         <v>45662.34861111111</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>45678.53756186798</v>
+        <v>45677.43048310962</v>
       </c>
       <c r="D47" t="n">
-        <v>23312.09</v>
+        <v>21717.9</v>
       </c>
       <c r="E47" t="n">
-        <v>23285.71</v>
+        <v>21691.41</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45662.35138888889</v>
+        <v>45662.35</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>45678.54159214268</v>
+        <v>45677.43410099015</v>
       </c>
       <c r="D48" t="n">
-        <v>23313.89</v>
+        <v>21721.11</v>
       </c>
       <c r="E48" t="n">
-        <v>23289.18</v>
+        <v>21695.68</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45662.35277777778</v>
+        <v>45662.35138888889</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>45679.29166666666</v>
+        <v>45677.43877493078</v>
       </c>
       <c r="D49" t="n">
-        <v>24392</v>
+        <v>21725.84</v>
       </c>
       <c r="E49" t="n">
-        <v>23286.55</v>
+        <v>21696.42</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2222,16 +2222,16 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45662.35555555556</v>
+        <v>45662.35277777778</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>45679.29528940734</v>
+        <v>45677.44257253456</v>
       </c>
       <c r="D50" t="n">
-        <v>24393.22</v>
+        <v>21729.3</v>
       </c>
       <c r="E50" t="n">
-        <v>24363.93</v>
+        <v>21703.32</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2246,16 +2246,16 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45662.35694444444</v>
+        <v>45662.35555555556</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>45679.29823183955</v>
+        <v>45677.44671235355</v>
       </c>
       <c r="D51" t="n">
-        <v>24395.45</v>
+        <v>21731.27</v>
       </c>
       <c r="E51" t="n">
-        <v>24368.49</v>
+        <v>21705.91</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45662.35833333333</v>
+        <v>45662.35694444444</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>45679.30286373736</v>
+        <v>45677.44981649565</v>
       </c>
       <c r="D52" t="n">
-        <v>24400.12</v>
+        <v>21733.74</v>
       </c>
       <c r="E52" t="n">
-        <v>24371.5</v>
+        <v>21706.66</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2297,13 +2297,13 @@
         <v>45662.35972222222</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>45679.30733133603</v>
+        <v>45677.45390445285</v>
       </c>
       <c r="D53" t="n">
-        <v>24404.56</v>
+        <v>21735.62</v>
       </c>
       <c r="E53" t="n">
-        <v>24375.82</v>
+        <v>21707.87</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45662.3625</v>
+        <v>45662.36111111111</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>45679.31113674448</v>
+        <v>45677.45685047198</v>
       </c>
       <c r="D54" t="n">
-        <v>24406.04</v>
+        <v>21737.86</v>
       </c>
       <c r="E54" t="n">
-        <v>24377.02</v>
+        <v>21711.54</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2342,16 +2342,16 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45662.36388888889</v>
+        <v>45662.3625</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>45679.3156680484</v>
+        <v>45677.4611666516</v>
       </c>
       <c r="D55" t="n">
-        <v>24410.56</v>
+        <v>21742.08</v>
       </c>
       <c r="E55" t="n">
-        <v>24381.76</v>
+        <v>21717.84</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45662.36666666667</v>
+        <v>45662.36388888889</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>45679.39527230465</v>
+        <v>45677.4657679312</v>
       </c>
       <c r="D56" t="n">
-        <v>24521.19</v>
+        <v>21746.71</v>
       </c>
       <c r="E56" t="n">
-        <v>24498.06</v>
+        <v>21719.51</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45662.36805555555</v>
+        <v>45662.36527777778</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>45679.39808909513</v>
+        <v>45677.46909221537</v>
       </c>
       <c r="D57" t="n">
-        <v>24523.25</v>
+        <v>21749.49</v>
       </c>
       <c r="E57" t="n">
-        <v>24497.84</v>
+        <v>21721.29</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45662.36944444444</v>
+        <v>45662.36666666667</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>45679.40209335557</v>
+        <v>45678.29604698024</v>
       </c>
       <c r="D58" t="n">
-        <v>24527.01</v>
+        <v>22938.31</v>
       </c>
       <c r="E58" t="n">
-        <v>24499.49</v>
+        <v>22909.59</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2438,20 +2438,20 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45662.35416666666</v>
+        <v>45662.36944444444</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>45679.40457191706</v>
+        <v>45678.30023809815</v>
       </c>
       <c r="D59" t="n">
-        <v>24552.58</v>
+        <v>22940.34</v>
       </c>
       <c r="E59" t="n">
-        <v>24334.01</v>
+        <v>22910.68</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2465,13 +2465,13 @@
         <v>45662.37222222222</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>45679.4054014357</v>
+        <v>45678.30489852621</v>
       </c>
       <c r="D60" t="n">
-        <v>24527.78</v>
+        <v>22943.05</v>
       </c>
       <c r="E60" t="n">
-        <v>24504.72</v>
+        <v>22915.49</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2486,20 +2486,20 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45662.37083333333</v>
+        <v>45662.34583333333</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>45679.47772115074</v>
+        <v>45678.30506665447</v>
       </c>
       <c r="D61" t="n">
-        <v>24633.92</v>
+        <v>22981.3</v>
       </c>
       <c r="E61" t="n">
-        <v>24606.84</v>
+        <v>21638.99</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2510,16 +2510,16 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45662.37361111111</v>
+        <v>45662.37083333333</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>45679.48015942366</v>
+        <v>45678.30954380152</v>
       </c>
       <c r="D62" t="n">
-        <v>24633.43</v>
+        <v>22951.74</v>
       </c>
       <c r="E62" t="n">
-        <v>24609.86</v>
+        <v>22924.32</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2537,13 +2537,13 @@
         <v>45662.37638888889</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>45679.4842906786</v>
+        <v>45678.37065837454</v>
       </c>
       <c r="D63" t="n">
-        <v>24635.38</v>
+        <v>23031.75</v>
       </c>
       <c r="E63" t="n">
-        <v>24608.39</v>
+        <v>23006.3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2558,16 +2558,16 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45662.35</v>
+        <v>45662.35416666666</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>45679.48824747477</v>
+        <v>45678.38042898908</v>
       </c>
       <c r="D64" t="n">
-        <v>24679.08</v>
+        <v>23077.82</v>
       </c>
       <c r="E64" t="n">
-        <v>24407.38</v>
+        <v>22824.77</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2582,20 +2582,20 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45662.37777777778</v>
+        <v>45662.35833333333</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>45679.48845420307</v>
+        <v>45678.48975022274</v>
       </c>
       <c r="D65" t="n">
-        <v>24639.37</v>
+        <v>23229.24</v>
       </c>
       <c r="E65" t="n">
-        <v>24608.73</v>
+        <v>22888.27</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2606,20 +2606,20 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45662.37916666667</v>
+        <v>45662.36805555555</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>45679.4929093571</v>
+        <v>45679.30275021361</v>
       </c>
       <c r="D66" t="n">
-        <v>24643.79</v>
+        <v>24385.96</v>
       </c>
       <c r="E66" t="n">
-        <v>24613.99</v>
+        <v>23088.95</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2630,20 +2630,20 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45662.38333333333</v>
+        <v>45662.375</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>45679.49740435466</v>
+        <v>45679.36613700811</v>
       </c>
       <c r="D67" t="n">
-        <v>24644.26</v>
+        <v>24467.24</v>
       </c>
       <c r="E67" t="n">
-        <v>24616.11</v>
+        <v>24203.75</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2654,16 +2654,16 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45662.38194444445</v>
+        <v>45662.37777777778</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>45679.50081486114</v>
+        <v>45679.45458931023</v>
       </c>
       <c r="D68" t="n">
-        <v>24651.17</v>
+        <v>24590.61</v>
       </c>
       <c r="E68" t="n">
-        <v>24624.37</v>
+        <v>24563.46</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2678,20 +2678,20 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45662.36111111111</v>
+        <v>45662.37916666667</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>45680.30615307333</v>
+        <v>45679.45848119786</v>
       </c>
       <c r="D69" t="n">
-        <v>25840.86</v>
+        <v>24594.21</v>
       </c>
       <c r="E69" t="n">
-        <v>24520</v>
+        <v>24564.99</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2702,20 +2702,20 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45662.38472222222</v>
+        <v>45662.37361111111</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>45680.40084635137</v>
+        <v>45679.46280503023</v>
       </c>
       <c r="D70" t="n">
-        <v>25943.22</v>
+        <v>24608.44</v>
       </c>
       <c r="E70" t="n">
-        <v>25912.95</v>
+        <v>24302.1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2726,20 +2726,20 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45662.38611111111</v>
+        <v>45662.38055555556</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>45680.40517113198</v>
+        <v>45679.46295694813</v>
       </c>
       <c r="D71" t="n">
-        <v>25947.45</v>
+        <v>24598.66</v>
       </c>
       <c r="E71" t="n">
-        <v>25921.01</v>
+        <v>23490.82</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2750,20 +2750,20 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45662.36527777778</v>
+        <v>45662.38194444445</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>45680.40836026006</v>
+        <v>45679.46685187928</v>
       </c>
       <c r="D72" t="n">
-        <v>25982.04</v>
+        <v>24602.27</v>
       </c>
       <c r="E72" t="n">
-        <v>25666.25</v>
+        <v>23498.98</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45662.3875</v>
+        <v>45662.38333333333</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>45680.40967682941</v>
+        <v>45679.47144544066</v>
       </c>
       <c r="D73" t="n">
-        <v>25951.93</v>
+        <v>24606.88</v>
       </c>
       <c r="E73" t="n">
-        <v>25924.95</v>
+        <v>24577.72</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2798,20 +2798,20 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45662.38055555556</v>
+        <v>45662.38611111111</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>45680.5357645696</v>
+        <v>45679.47506898885</v>
       </c>
       <c r="D74" t="n">
-        <v>26143.5</v>
+        <v>24608.1</v>
       </c>
       <c r="E74" t="n">
-        <v>25832.45</v>
+        <v>24577.89</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2822,20 +2822,20 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45662.375</v>
+        <v>45662.3875</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>45681.29936357489</v>
+        <v>45679.47922680012</v>
       </c>
       <c r="D75" t="n">
-        <v>27251.08</v>
+        <v>24612.09</v>
       </c>
       <c r="E75" t="n">
-        <v>25950.42</v>
+        <v>24585.72</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -2849,13 +2849,13 @@
         <v>45662.38888888889</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>45681.3021171319</v>
+        <v>45679.48314812974</v>
       </c>
       <c r="D76" t="n">
-        <v>27235.05</v>
+        <v>24615.73</v>
       </c>
       <c r="E76" t="n">
-        <v>27208.32</v>
+        <v>24588.25</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2873,13 +2873,13 @@
         <v>45662.39027777778</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>45681.30630891504</v>
+        <v>45679.48728703719</v>
       </c>
       <c r="D77" t="n">
-        <v>27239.08</v>
+        <v>24619.69</v>
       </c>
       <c r="E77" t="n">
-        <v>27211.24</v>
+        <v>24593.78</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2897,13 +2897,13 @@
         <v>45662.39166666667</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>45681.30929125974</v>
+        <v>45679.49073334755</v>
       </c>
       <c r="D78" t="n">
-        <v>27241.38</v>
+        <v>24622.66</v>
       </c>
       <c r="E78" t="n">
-        <v>27213.53</v>
+        <v>24601.31</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45662.39305555556</v>
+        <v>45662.39583333334</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>45681.31366135218</v>
+        <v>45680.29576971807</v>
       </c>
       <c r="D79" t="n">
-        <v>27245.67</v>
+        <v>25775.91</v>
       </c>
       <c r="E79" t="n">
-        <v>27217.19</v>
+        <v>25749.21</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45662.39444444444</v>
+        <v>45662.4</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>45681.31803175672</v>
+        <v>45680.29836126349</v>
       </c>
       <c r="D80" t="n">
-        <v>27249.97</v>
+        <v>25773.64</v>
       </c>
       <c r="E80" t="n">
-        <v>27222.06</v>
+        <v>25747.38</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45662.39722222222</v>
+        <v>45662.40138888889</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>45681.3209855744</v>
+        <v>45680.30192706605</v>
       </c>
       <c r="D81" t="n">
-        <v>27250.22</v>
+        <v>25776.77</v>
       </c>
       <c r="E81" t="n">
-        <v>27225.54</v>
+        <v>25747.45</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45662.39861111111</v>
+        <v>45662.40416666667</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>45681.3242839368</v>
+        <v>45680.30552237033</v>
       </c>
       <c r="D82" t="n">
-        <v>27252.97</v>
+        <v>25777.95</v>
       </c>
       <c r="E82" t="n">
-        <v>27226.11</v>
+        <v>25754.2</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3014,20 +3014,20 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45662.4</v>
+        <v>45662.38472222222</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>45681.32760307437</v>
+        <v>45680.30775151414</v>
       </c>
       <c r="D83" t="n">
-        <v>27255.75</v>
+        <v>25809.16</v>
       </c>
       <c r="E83" t="n">
-        <v>27231.83</v>
+        <v>24537.75</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45662.40277777778</v>
+        <v>45662.40694444445</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>45681.33119633021</v>
+        <v>45680.30977670962</v>
       </c>
       <c r="D84" t="n">
-        <v>27256.92</v>
+        <v>25780.08</v>
       </c>
       <c r="E84" t="n">
-        <v>27228.59</v>
+        <v>25751.57</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3062,16 +3062,16 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45662.40555555555</v>
+        <v>45662.40833333333</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>45681.33461168112</v>
+        <v>45680.31349175517</v>
       </c>
       <c r="D85" t="n">
-        <v>27257.84</v>
+        <v>25783.43</v>
       </c>
       <c r="E85" t="n">
-        <v>27235.5</v>
+        <v>25754.58</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45662.40416666667</v>
+        <v>45662.40972222222</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>45681.33846355641</v>
+        <v>45680.31586802262</v>
       </c>
       <c r="D86" t="n">
-        <v>27265.39</v>
+        <v>25784.85</v>
       </c>
       <c r="E86" t="n">
-        <v>27234.89</v>
+        <v>25764.63</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45662.40694444445</v>
+        <v>45662.41111111111</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>45681.34197540774</v>
+        <v>45680.3193618877</v>
       </c>
       <c r="D87" t="n">
-        <v>27266.44</v>
+        <v>25787.88</v>
       </c>
       <c r="E87" t="n">
-        <v>27237.76</v>
+        <v>25761.42</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3134,16 +3134,16 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45662.40833333333</v>
+        <v>45662.4125</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>45681.34628781332</v>
+        <v>45680.322826858</v>
       </c>
       <c r="D88" t="n">
-        <v>27270.65</v>
+        <v>25790.87</v>
       </c>
       <c r="E88" t="n">
-        <v>27242.27</v>
+        <v>25762.06</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3158,16 +3158,16 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45662.40972222222</v>
+        <v>45662.41388888889</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>45681.34972006597</v>
+        <v>45680.32727616818</v>
       </c>
       <c r="D89" t="n">
-        <v>27273.6</v>
+        <v>25795.28</v>
       </c>
       <c r="E89" t="n">
-        <v>27244.35</v>
+        <v>25767.63</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3182,16 +3182,16 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45662.4125</v>
+        <v>45662.41527777778</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>45681.35353542436</v>
+        <v>45680.33194784635</v>
       </c>
       <c r="D90" t="n">
-        <v>27275.09</v>
+        <v>25800</v>
       </c>
       <c r="E90" t="n">
-        <v>27248.95</v>
+        <v>25773.35</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3206,16 +3206,16 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45662.41388888889</v>
+        <v>45662.41666666666</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>45681.35595963308</v>
+        <v>45680.33647128829</v>
       </c>
       <c r="D91" t="n">
-        <v>27276.58</v>
+        <v>25804.52</v>
       </c>
       <c r="E91" t="n">
-        <v>27248.41</v>
+        <v>25779.71</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3230,20 +3230,20 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45662.41527777778</v>
+        <v>45662.39444444444</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>45681.36052819547</v>
+        <v>45680.45165215246</v>
       </c>
       <c r="D92" t="n">
-        <v>27281.16</v>
+        <v>26002.38</v>
       </c>
       <c r="E92" t="n">
-        <v>27254.37</v>
+        <v>25674.61</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -3254,20 +3254,20 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45662.41111111111</v>
+        <v>45662.39305555556</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>45682.4118632898</v>
+        <v>45681.30395412225</v>
       </c>
       <c r="D93" t="n">
-        <v>28801.08</v>
+        <v>27231.69</v>
       </c>
       <c r="E93" t="n">
-        <v>28502.08</v>
+        <v>25809.91</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -3278,16 +3278,16 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45662.41666666666</v>
+        <v>45662.41805555556</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>45682.41508173538</v>
+        <v>45681.4000094676</v>
       </c>
       <c r="D94" t="n">
-        <v>28797.72</v>
+        <v>27334.01</v>
       </c>
       <c r="E94" t="n">
-        <v>28772.41</v>
+        <v>27305.33</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3302,20 +3302,20 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45662.41805555556</v>
+        <v>45662.39722222222</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>45682.41875947017</v>
+        <v>45681.41150844435</v>
       </c>
       <c r="D95" t="n">
-        <v>28801.01</v>
+        <v>27380.57</v>
       </c>
       <c r="E95" t="n">
-        <v>28775.32</v>
+        <v>27061.64</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -3326,20 +3326,20 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45662.41944444444</v>
+        <v>45662.39861111111</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>45682.42328160448</v>
+        <v>45681.5152986481</v>
       </c>
       <c r="D96" t="n">
-        <v>28805.53</v>
+        <v>27528.03</v>
       </c>
       <c r="E96" t="n">
-        <v>28777.75</v>
+        <v>27220.58</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45662.42361111111</v>
+        <v>45662.41944444444</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>45682.42780392143</v>
+        <v>45682.29557146539</v>
       </c>
       <c r="D97" t="n">
-        <v>28806.04</v>
+        <v>28621.62</v>
       </c>
       <c r="E97" t="n">
-        <v>28781.2</v>
+        <v>28592.06</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3374,20 +3374,20 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45662.42222222222</v>
+        <v>45662.40555555555</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>45682.50846915448</v>
+        <v>45682.30482944068</v>
       </c>
       <c r="D98" t="n">
-        <v>28924.2</v>
+        <v>28654.95</v>
       </c>
       <c r="E98" t="n">
-        <v>27819.88</v>
+        <v>27387.42</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -3398,20 +3398,644 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
+        <v>45662.42083333333</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>45682.36125961172</v>
+      </c>
+      <c r="D99" t="n">
+        <v>28714.21</v>
+      </c>
+      <c r="E99" t="n">
+        <v>28689.41</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>45662.42222222222</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>45682.36506481839</v>
+      </c>
+      <c r="D100" t="n">
+        <v>28717.69</v>
+      </c>
+      <c r="E100" t="n">
+        <v>28688.22</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>45662.42361111111</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>45682.36950473118</v>
+      </c>
+      <c r="D101" t="n">
+        <v>28722.09</v>
+      </c>
+      <c r="E101" t="n">
+        <v>28690.55</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>45662.40277777778</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>45682.37171391879</v>
+      </c>
+      <c r="D102" t="n">
+        <v>28755.27</v>
+      </c>
+      <c r="E102" t="n">
+        <v>28515.25</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
         <v>45662.425</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>45682.511289335</v>
-      </c>
-      <c r="D99" t="n">
-        <v>28924.26</v>
-      </c>
-      <c r="E99" t="n">
-        <v>28903.7</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+      <c r="C103" s="2" t="n">
+        <v>45682.37232945213</v>
+      </c>
+      <c r="D103" t="n">
+        <v>28724.15</v>
+      </c>
+      <c r="E103" t="n">
+        <v>28698.87</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>45662.42638888889</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>45682.37644474079</v>
+      </c>
+      <c r="D104" t="n">
+        <v>28728.08</v>
+      </c>
+      <c r="E104" t="n">
+        <v>28700.18</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>45662.42777777778</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>45682.3806963802</v>
+      </c>
+      <c r="D105" t="n">
+        <v>28732.2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>28704.42</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>45662.42916666667</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>45682.38506751259</v>
+      </c>
+      <c r="D106" t="n">
+        <v>28736.5</v>
+      </c>
+      <c r="E106" t="n">
+        <v>28709.36</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>45662.43055555555</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>45682.38970902534</v>
+      </c>
+      <c r="D107" t="n">
+        <v>28741.18</v>
+      </c>
+      <c r="E107" t="n">
+        <v>28712.76</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>45662.43194444444</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>45682.39383160766</v>
+      </c>
+      <c r="D108" t="n">
+        <v>28745.12</v>
+      </c>
+      <c r="E108" t="n">
+        <v>28715.49</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>45662.43333333333</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>45682.39839205483</v>
+      </c>
+      <c r="D109" t="n">
+        <v>28749.68</v>
+      </c>
+      <c r="E109" t="n">
+        <v>28721.07</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>45662.43611111111</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>45682.40189128138</v>
+      </c>
+      <c r="D110" t="n">
+        <v>28750.72</v>
+      </c>
+      <c r="E110" t="n">
+        <v>28722.48</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>45662.43472222222</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>45682.50878649591</v>
+      </c>
+      <c r="D111" t="n">
+        <v>28906.65</v>
+      </c>
+      <c r="E111" t="n">
+        <v>27638.83</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>45662.44027777778</v>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>45683.29476731822</v>
+      </c>
+      <c r="D112" t="n">
+        <v>30030.46</v>
+      </c>
+      <c r="E112" t="n">
+        <v>30006.79</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>45662.44305555556</v>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>45683.298002282</v>
+      </c>
+      <c r="D113" t="n">
+        <v>30031.12</v>
+      </c>
+      <c r="E113" t="n">
+        <v>30004.98</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>45662.44444444445</v>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>45683.3022160192</v>
+      </c>
+      <c r="D114" t="n">
+        <v>30035.19</v>
+      </c>
+      <c r="E114" t="n">
+        <v>30008.65</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>45662.44583333333</v>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>45683.30569821764</v>
+      </c>
+      <c r="D115" t="n">
+        <v>30038.21</v>
+      </c>
+      <c r="E115" t="n">
+        <v>30012.82</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>45662.4375</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>45683.30742214988</v>
+      </c>
+      <c r="D116" t="n">
+        <v>30052.69</v>
+      </c>
+      <c r="E116" t="n">
+        <v>27785.09</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>45662.44861111111</v>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>45683.30945422715</v>
+      </c>
+      <c r="D117" t="n">
+        <v>30039.61</v>
+      </c>
+      <c r="E117" t="n">
+        <v>30014.03</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>45662.45277777778</v>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>45683.31297951594</v>
+      </c>
+      <c r="D118" t="n">
+        <v>30038.69</v>
+      </c>
+      <c r="E118" t="n">
+        <v>30011.46</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>45662.45416666667</v>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>45683.3914549181</v>
+      </c>
+      <c r="D119" t="n">
+        <v>30149.7</v>
+      </c>
+      <c r="E119" t="n">
+        <v>30121.08</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>45662.45555555556</v>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>45683.39545692968</v>
+      </c>
+      <c r="D120" t="n">
+        <v>30153.46</v>
+      </c>
+      <c r="E120" t="n">
+        <v>30129.32</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>45662.44166666667</v>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>45683.40281377276</v>
+      </c>
+      <c r="D121" t="n">
+        <v>30184.05</v>
+      </c>
+      <c r="E121" t="n">
+        <v>29954.72</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>45662.44722222222</v>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>45683.48528964628</v>
+      </c>
+      <c r="D122" t="n">
+        <v>30294.82</v>
+      </c>
+      <c r="E122" t="n">
+        <v>30057.57</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>45662.43888888889</v>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>45683.53375720033</v>
+      </c>
+      <c r="D123" t="n">
+        <v>30376.61</v>
+      </c>
+      <c r="E123" t="n">
+        <v>29038.09</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>45662.45138888889</v>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>45684.30524191434</v>
+      </c>
+      <c r="D124" t="n">
+        <v>31469.55</v>
+      </c>
+      <c r="E124" t="n">
+        <v>30217.91</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>45662.45</v>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>45684.40300360583</v>
+      </c>
+      <c r="D125" t="n">
+        <v>31612.33</v>
+      </c>
+      <c r="E125" t="n">
+        <v>31276.63</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -3458,7 +4082,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4">
@@ -3468,7 +4092,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.65000000000001</v>
+        <v>96.77</v>
       </c>
     </row>
     <row r="5">
@@ -3478,7 +4102,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.710000000000001</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="6">
@@ -3488,7 +4112,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.81</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="7">
@@ -3498,7 +4122,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55.56</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>

--- a/5.5.13 Real Property-Monthly Reviews-2_results.xlsx
+++ b/5.5.13 Real Property-Monthly Reviews-2_results.xlsx
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09</v>
+        <v>18.28</v>
       </c>
     </row>
   </sheetData>
@@ -573,40 +573,40 @@
         <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E2" t="n">
-        <v>24.8</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>59.95</v>
+        <v>36.79</v>
       </c>
       <c r="G2" t="n">
-        <v>31612.33</v>
+        <v>40128.31</v>
       </c>
       <c r="H2" t="n">
-        <v>18879.43</v>
+        <v>22875.19</v>
       </c>
       <c r="I2" t="n">
-        <v>23077.82</v>
+        <v>24540.37</v>
       </c>
       <c r="J2" t="n">
-        <v>10449.24</v>
+        <v>11370.14</v>
       </c>
       <c r="K2" t="n">
-        <v>30030.93</v>
+        <v>35881.35</v>
       </c>
       <c r="L2" t="n">
-        <v>2304145.7</v>
+        <v>2567094.41</v>
       </c>
       <c r="M2" t="n">
-        <v>32.97</v>
+        <v>24.57</v>
       </c>
       <c r="N2" t="n">
-        <v>31276.63</v>
+        <v>40113.93</v>
       </c>
       <c r="O2" t="n">
-        <v>18581.82</v>
+        <v>22717.65</v>
       </c>
     </row>
     <row r="3">
@@ -672,43 +672,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D4" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>5.19</v>
+        <v>5.16</v>
       </c>
       <c r="G4" t="n">
         <v>9.58</v>
       </c>
       <c r="H4" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>8.24</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K4" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
       <c r="L4" t="n">
-        <v>10183752.51</v>
+        <v>6529118.03</v>
       </c>
       <c r="M4" t="n">
-        <v>6.21</v>
+        <v>5.92</v>
       </c>
       <c r="N4" t="n">
-        <v>20332.4</v>
+        <v>29988.34</v>
       </c>
       <c r="O4" t="n">
-        <v>10255.54</v>
+        <v>13084.4</v>
       </c>
     </row>
     <row r="5">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D5" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
@@ -774,43 +774,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D6" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="G6" t="n">
-        <v>6.73</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
         <v>5.53</v>
       </c>
       <c r="I6" t="n">
-        <v>5.65</v>
+        <v>5.86</v>
       </c>
       <c r="J6" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="L6" t="n">
-        <v>3098701.11</v>
+        <v>1750713.92</v>
       </c>
       <c r="M6" t="n">
-        <v>32.97</v>
+        <v>24.57</v>
       </c>
       <c r="N6" t="n">
-        <v>27225.48</v>
+        <v>35840.76</v>
       </c>
       <c r="O6" t="n">
-        <v>16570.59</v>
+        <v>20596.63</v>
       </c>
     </row>
     <row r="7">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D7" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E7" t="n">
         <v>100</v>
@@ -852,16 +852,16 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8.57</v>
+        <v>1316.14</v>
       </c>
       <c r="M7" t="n">
-        <v>8.57</v>
+        <v>6.31</v>
       </c>
       <c r="N7" t="n">
-        <v>8.57</v>
+        <v>1085.12</v>
       </c>
       <c r="O7" t="n">
-        <v>8.57</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="8">
@@ -876,43 +876,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>70.27</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>161.49</v>
+        <v>162.38</v>
       </c>
       <c r="H8" t="n">
-        <v>126.06</v>
+        <v>126.69</v>
       </c>
       <c r="I8" t="n">
-        <v>133.75</v>
+        <v>126.08</v>
       </c>
       <c r="J8" t="n">
-        <v>27.1</v>
+        <v>20.31</v>
       </c>
       <c r="K8" t="n">
-        <v>156.43</v>
+        <v>156.88</v>
       </c>
       <c r="L8" t="n">
-        <v>1031770.38</v>
+        <v>512991.15</v>
       </c>
       <c r="M8" t="n">
-        <v>1510.3</v>
+        <v>58.03</v>
       </c>
       <c r="N8" t="n">
-        <v>27125.38</v>
+        <v>31774.25</v>
       </c>
       <c r="O8" t="n">
-        <v>19106.86</v>
+        <v>20519.65</v>
       </c>
     </row>
     <row r="9">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -978,43 +978,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>7.59</v>
+        <v>6.31</v>
       </c>
       <c r="G10" t="n">
-        <v>12.07</v>
+        <v>11.97</v>
       </c>
       <c r="H10" t="n">
-        <v>10.36</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>10.58</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="K10" t="n">
-        <v>11.85</v>
+        <v>11.81</v>
       </c>
       <c r="L10" t="n">
-        <v>129.44</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.83</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,2976 +1066,2712 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-1</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45662.29166666666</v>
+        <v>45663.29166666666</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45662.33329752198</v>
+        <v>45663.31721341277</v>
       </c>
       <c r="D2" t="n">
-        <v>59.95</v>
+        <v>36.79</v>
       </c>
       <c r="E2" t="n">
-        <v>32.97</v>
+        <v>24.57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-2</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45662.29305555556</v>
+        <v>45663.29305555556</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45662.37334402597</v>
+        <v>45663.43960284361</v>
       </c>
       <c r="D3" t="n">
-        <v>115.62</v>
+        <v>211.03</v>
       </c>
       <c r="E3" t="n">
-        <v>87.23</v>
+        <v>71.36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45662.29583333333</v>
+        <v>45663.29444444444</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45662.40163947275</v>
+        <v>45664.2971430707</v>
       </c>
       <c r="D4" t="n">
-        <v>152.36</v>
+        <v>1443.89</v>
       </c>
       <c r="E4" t="n">
-        <v>125.87</v>
+        <v>239.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45662.29722222222</v>
+        <v>45663.29583333333</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45662.43762263396</v>
+        <v>45664.31772866953</v>
       </c>
       <c r="D5" t="n">
-        <v>202.18</v>
+        <v>1471.53</v>
       </c>
       <c r="E5" t="n">
-        <v>179.17</v>
+        <v>1457.31</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-5</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45662.29861111111</v>
+        <v>45663.29722222222</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45662.46990041722</v>
+        <v>45664.3554593779</v>
       </c>
       <c r="D6" t="n">
-        <v>246.66</v>
+        <v>1523.86</v>
       </c>
       <c r="E6" t="n">
-        <v>219.67</v>
+        <v>1510.88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-6</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45662.3</v>
+        <v>45663.29861111111</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>45662.51885033459</v>
+        <v>45664.38601615631</v>
       </c>
       <c r="D7" t="n">
-        <v>315.14</v>
+        <v>1565.86</v>
       </c>
       <c r="E7" t="n">
-        <v>285.13</v>
+        <v>1550.43</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-7</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45662.30138888889</v>
+        <v>45663.3</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45662.5399183164</v>
+        <v>45664.41771524574</v>
       </c>
       <c r="D8" t="n">
-        <v>343.48</v>
+        <v>1609.51</v>
       </c>
       <c r="E8" t="n">
-        <v>316.25</v>
+        <v>1593.42</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45662.30277777778</v>
+        <v>45663.30138888889</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45663.31580679751</v>
+        <v>45664.51319002151</v>
       </c>
       <c r="D9" t="n">
-        <v>1458.76</v>
+        <v>1744.99</v>
       </c>
       <c r="E9" t="n">
-        <v>1431.38</v>
+        <v>1642.04</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-103</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45662.30416666667</v>
+        <v>45663.43333333333</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45663.35101653879</v>
+        <v>45666.37843254983</v>
       </c>
       <c r="D10" t="n">
-        <v>1507.46</v>
+        <v>4240.94</v>
       </c>
       <c r="E10" t="n">
-        <v>1480.52</v>
+        <v>4227.79</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-9</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45662.30555555555</v>
+        <v>45663.30277777778</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>45663.39079347986</v>
+        <v>45666.40604065492</v>
       </c>
       <c r="D11" t="n">
-        <v>1562.74</v>
+        <v>4468.7</v>
       </c>
       <c r="E11" t="n">
-        <v>1532.57</v>
+        <v>4455.27</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45662.30833333333</v>
+        <v>45663.30416666667</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45663.43154756449</v>
+        <v>45667.29166666666</v>
       </c>
       <c r="D12" t="n">
-        <v>1617.43</v>
+        <v>5742</v>
       </c>
       <c r="E12" t="n">
-        <v>1589.82</v>
+        <v>5573.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-11</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45662.29444444444</v>
+        <v>45663.30555555555</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>45663.5338707749</v>
+        <v>45667.31224586003</v>
       </c>
       <c r="D13" t="n">
-        <v>1784.77</v>
+        <v>5769.63</v>
       </c>
       <c r="E13" t="n">
-        <v>1532.25</v>
+        <v>5757.25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45662.31111111111</v>
+        <v>45663.30694444444</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>45664.3203193547</v>
+        <v>45667.33770677419</v>
       </c>
       <c r="D14" t="n">
-        <v>2893.26</v>
+        <v>5804.3</v>
       </c>
       <c r="E14" t="n">
-        <v>2864.74</v>
+        <v>5791.23</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-13</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45662.3125</v>
+        <v>45663.30833333333</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>45664.34962421956</v>
+        <v>45667.36589191009</v>
       </c>
       <c r="D15" t="n">
-        <v>2933.46</v>
+        <v>5842.88</v>
       </c>
       <c r="E15" t="n">
-        <v>2907.38</v>
+        <v>5827.73</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-181</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45662.31527777778</v>
+        <v>45664.29166666666</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>45664.41355094349</v>
+        <v>45670.44068827211</v>
       </c>
       <c r="D16" t="n">
-        <v>3021.51</v>
+        <v>8854.59</v>
       </c>
       <c r="E16" t="n">
-        <v>2990.55</v>
+        <v>8839.190000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-14</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45662.31666666667</v>
+        <v>45663.30972222222</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>45664.43969734229</v>
+        <v>45670.46319867545</v>
       </c>
       <c r="D17" t="n">
-        <v>3057.16</v>
+        <v>10301.01</v>
       </c>
       <c r="E17" t="n">
-        <v>3029.78</v>
+        <v>10288.28</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45662.31805555556</v>
+        <v>45663.31111111111</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>45664.46696351265</v>
+        <v>45671.29768164405</v>
       </c>
       <c r="D18" t="n">
-        <v>3094.43</v>
+        <v>11500.66</v>
       </c>
       <c r="E18" t="n">
-        <v>3065.71</v>
+        <v>10330.58</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-16</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45662.32222222222</v>
+        <v>45663.3125</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>45665.30706725767</v>
+        <v>45671.31761670134</v>
       </c>
       <c r="D19" t="n">
-        <v>4298.18</v>
+        <v>11527.37</v>
       </c>
       <c r="E19" t="n">
-        <v>4270.89</v>
+        <v>11514.26</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45662.32361111111</v>
+        <v>45663.31388888889</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>45665.33880627694</v>
+        <v>45671.34073293558</v>
       </c>
       <c r="D20" t="n">
-        <v>4341.88</v>
+        <v>11558.66</v>
       </c>
       <c r="E20" t="n">
-        <v>4312.75</v>
+        <v>11545.99</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-18</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45662.325</v>
+        <v>45663.31527777778</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>45665.36845109234</v>
+        <v>45671.38452700573</v>
       </c>
       <c r="D21" t="n">
-        <v>4382.57</v>
+        <v>11619.72</v>
       </c>
       <c r="E21" t="n">
-        <v>4353.12</v>
+        <v>11605.45</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-19</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45662.31388888889</v>
+        <v>45663.31666666667</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45665.49950817604</v>
+        <v>45671.41943317295</v>
       </c>
       <c r="D22" t="n">
-        <v>4587.29</v>
+        <v>11667.98</v>
       </c>
       <c r="E22" t="n">
-        <v>4318.61</v>
+        <v>11652.76</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-20</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45662.30694444444</v>
+        <v>45663.31805555556</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>45666.30669177544</v>
+        <v>45671.43897879779</v>
       </c>
       <c r="D23" t="n">
-        <v>5759.64</v>
+        <v>11694.13</v>
       </c>
       <c r="E23" t="n">
-        <v>4419.3</v>
+        <v>11682.02</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-21</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45662.32777777778</v>
+        <v>45663.31944444445</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>45666.31027586611</v>
+        <v>45671.46540720287</v>
       </c>
       <c r="D24" t="n">
-        <v>5734.8</v>
+        <v>11730.19</v>
       </c>
       <c r="E24" t="n">
-        <v>5711.16</v>
+        <v>11717.79</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-22</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45662.32638888889</v>
+        <v>45663.32083333333</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>45666.33877452159</v>
+        <v>45672.29859885221</v>
       </c>
       <c r="D25" t="n">
-        <v>5777.84</v>
+        <v>12927.98</v>
       </c>
       <c r="E25" t="n">
-        <v>5749.81</v>
+        <v>11769.95</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-23</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45662.32916666667</v>
+        <v>45663.32222222222</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>45666.3760189571</v>
+        <v>45672.31661976408</v>
       </c>
       <c r="D26" t="n">
-        <v>5827.47</v>
+        <v>12951.93</v>
       </c>
       <c r="E26" t="n">
-        <v>5797.79</v>
+        <v>12936.38</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-24</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45662.33194444444</v>
+        <v>45663.32361111111</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45666.39543306366</v>
+        <v>45672.36051535398</v>
       </c>
       <c r="D27" t="n">
-        <v>5851.42</v>
+        <v>13013.14</v>
       </c>
       <c r="E27" t="n">
-        <v>5825.24</v>
+        <v>13000.27</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-25</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45662.33055555556</v>
+        <v>45663.325</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>45666.4291758629</v>
+        <v>45672.38082167129</v>
       </c>
       <c r="D28" t="n">
-        <v>5902.01</v>
+        <v>13040.38</v>
       </c>
       <c r="E28" t="n">
-        <v>5873.09</v>
+        <v>13027.22</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45662.33333333334</v>
+        <v>45663.32638888889</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>45666.44954801867</v>
+        <v>45672.40704021512</v>
       </c>
       <c r="D29" t="n">
-        <v>5927.35</v>
+        <v>13076.14</v>
       </c>
       <c r="E29" t="n">
-        <v>5901.38</v>
+        <v>13065.1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-27</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45662.30972222222</v>
+        <v>45663.32777777778</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45667.30633220963</v>
+        <v>45672.43373454718</v>
       </c>
       <c r="D30" t="n">
-        <v>7195.12</v>
+        <v>13112.58</v>
       </c>
       <c r="E30" t="n">
-        <v>5796.98</v>
+        <v>13097.99</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-28</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45662.48888888889</v>
+        <v>45663.32916666667</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>45667.37023438902</v>
+        <v>45672.45489404738</v>
       </c>
       <c r="D31" t="n">
-        <v>7029.14</v>
+        <v>13141.05</v>
       </c>
       <c r="E31" t="n">
-        <v>5687.5</v>
+        <v>13128.89</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-29</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45662.32083333333</v>
+        <v>45663.33055555556</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>45667.47586051536</v>
+        <v>45672.50437229722</v>
       </c>
       <c r="D32" t="n">
-        <v>7423.24</v>
+        <v>13210.3</v>
       </c>
       <c r="E32" t="n">
-        <v>7158.56</v>
+        <v>13195.03</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-30</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45662.33611111111</v>
+        <v>45663.33194444444</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>45667.48772982143</v>
+        <v>45672.53300122751</v>
       </c>
       <c r="D33" t="n">
-        <v>7418.33</v>
+        <v>13249.52</v>
       </c>
       <c r="E33" t="n">
-        <v>7389.91</v>
+        <v>13236.18</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-31</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45662.3375</v>
+        <v>45663.33333333334</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>45667.52647083604</v>
+        <v>45673.38205540463</v>
       </c>
       <c r="D34" t="n">
-        <v>7472.12</v>
+        <v>14470.16</v>
       </c>
       <c r="E34" t="n">
-        <v>7444.75</v>
+        <v>14353.37</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-32</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45662.34027777778</v>
+        <v>45663.33472222222</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>45668.41375448016</v>
+        <v>45673.40792404069</v>
       </c>
       <c r="D35" t="n">
-        <v>8745.809999999999</v>
+        <v>14505.41</v>
       </c>
       <c r="E35" t="n">
-        <v>8720.639999999999</v>
+        <v>14490.48</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-33</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45662.31944444445</v>
+        <v>45663.33611111111</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>45668.41976485375</v>
+        <v>45673.51901447696</v>
       </c>
       <c r="D36" t="n">
-        <v>8784.459999999999</v>
+        <v>14663.38</v>
       </c>
       <c r="E36" t="n">
-        <v>8457.84</v>
+        <v>14533.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-34</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45662.33888888889</v>
+        <v>45663.3375</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>45668.44414685827</v>
+        <v>45674.295780187</v>
       </c>
       <c r="D37" t="n">
-        <v>8791.57</v>
+        <v>15779.92</v>
       </c>
       <c r="E37" t="n">
-        <v>8764.33</v>
+        <v>15766.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-35</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45662.34166666667</v>
+        <v>45663.33888888889</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>45668.4639501508</v>
+        <v>45674.32342070774</v>
       </c>
       <c r="D38" t="n">
-        <v>8816.09</v>
+        <v>15817.73</v>
       </c>
       <c r="E38" t="n">
-        <v>8794.24</v>
+        <v>15803.71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-36</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45662.34305555555</v>
+        <v>45663.34027777778</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>45668.50091386359</v>
+        <v>45674.35048978139</v>
       </c>
       <c r="D39" t="n">
-        <v>8867.32</v>
+        <v>15854.71</v>
       </c>
       <c r="E39" t="n">
-        <v>8841.049999999999</v>
+        <v>15839.6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-37</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45662.33472222222</v>
+        <v>45663.34166666667</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>45669.30678219995</v>
+        <v>45674.38200978176</v>
       </c>
       <c r="D40" t="n">
-        <v>10039.77</v>
+        <v>15898.09</v>
       </c>
       <c r="E40" t="n">
-        <v>7766.26</v>
+        <v>15883.09</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-335</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45662.34444444445</v>
+        <v>45664.50555555556</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>45669.53506792918</v>
+        <v>45677.39655038607</v>
       </c>
       <c r="D41" t="n">
-        <v>10354.5</v>
+        <v>18563.03</v>
       </c>
       <c r="E41" t="n">
-        <v>9250.26</v>
+        <v>18547.43</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-38</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45662.85138888889</v>
+        <v>45663.34305555555</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>45670.41012530989</v>
+        <v>45677.42384014429</v>
       </c>
       <c r="D42" t="n">
-        <v>10884.58</v>
+        <v>20276.33</v>
       </c>
       <c r="E42" t="n">
-        <v>8970.440000000001</v>
+        <v>20263.99</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-39</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45662.69305555556</v>
+        <v>45663.34444444445</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>45674.41309944067</v>
+        <v>45677.44931287152</v>
       </c>
       <c r="D43" t="n">
-        <v>16876.86</v>
+        <v>20311.01</v>
       </c>
       <c r="E43" t="n">
-        <v>14727.07</v>
+        <v>20298.97</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-40</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45662.88472222222</v>
+        <v>45663.34583333333</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>45675.41094876696</v>
+        <v>45677.47497442387</v>
       </c>
       <c r="D44" t="n">
-        <v>18037.77</v>
+        <v>20345.96</v>
       </c>
       <c r="E44" t="n">
-        <v>16140.3</v>
+        <v>20335.46</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-41</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45662.83333333334</v>
+        <v>45663.34722222222</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>45677.36096354036</v>
+        <v>45677.50290023257</v>
       </c>
       <c r="D45" t="n">
-        <v>20919.79</v>
+        <v>20384.18</v>
       </c>
       <c r="E45" t="n">
-        <v>19061.21</v>
+        <v>20369.65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-42</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45662.34722222222</v>
+        <v>45663.34861111111</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>45677.42750575664</v>
+        <v>45678.29806088944</v>
       </c>
       <c r="D46" t="n">
-        <v>21715.61</v>
+        <v>21527.21</v>
       </c>
       <c r="E46" t="n">
-        <v>21688.09</v>
+        <v>20412.05</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-43</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45662.34861111111</v>
+        <v>45663.35</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>45677.43048310962</v>
+        <v>45678.32033430828</v>
       </c>
       <c r="D47" t="n">
-        <v>21717.9</v>
+        <v>21557.28</v>
       </c>
       <c r="E47" t="n">
-        <v>21691.41</v>
+        <v>21542.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-44</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45662.35</v>
+        <v>45663.35138888889</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>45677.43410099015</v>
+        <v>45678.33959309206</v>
       </c>
       <c r="D48" t="n">
-        <v>21721.11</v>
+        <v>21583.01</v>
       </c>
       <c r="E48" t="n">
-        <v>21695.68</v>
+        <v>20492.94</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-45</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45662.35138888889</v>
+        <v>45663.35277777778</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>45677.43877493078</v>
+        <v>45678.36494839615</v>
       </c>
       <c r="D49" t="n">
-        <v>21725.84</v>
+        <v>21617.53</v>
       </c>
       <c r="E49" t="n">
-        <v>21696.42</v>
+        <v>21603.65</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-46</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45662.35277777778</v>
+        <v>45663.35416666666</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>45677.44257253456</v>
+        <v>45678.47365094475</v>
       </c>
       <c r="D50" t="n">
-        <v>21729.3</v>
+        <v>21772.06</v>
       </c>
       <c r="E50" t="n">
-        <v>21703.32</v>
+        <v>21644.66</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-47</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45662.35555555556</v>
+        <v>45663.35555555556</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>45677.44671235355</v>
+        <v>45678.50031963876</v>
       </c>
       <c r="D51" t="n">
-        <v>21731.27</v>
+        <v>21808.46</v>
       </c>
       <c r="E51" t="n">
-        <v>21705.91</v>
+        <v>21792.52</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-48</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45662.35694444444</v>
+        <v>45663.35694444444</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>45677.44981649565</v>
+        <v>45678.52839636653</v>
       </c>
       <c r="D52" t="n">
-        <v>21733.74</v>
+        <v>21846.89</v>
       </c>
       <c r="E52" t="n">
-        <v>21706.66</v>
+        <v>21832.74</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-49</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45662.35972222222</v>
+        <v>45663.35833333333</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>45677.45390445285</v>
+        <v>45679.30709659647</v>
       </c>
       <c r="D53" t="n">
-        <v>21735.62</v>
+        <v>22966.22</v>
       </c>
       <c r="E53" t="n">
-        <v>21707.87</v>
+        <v>22950.99</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-50</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45662.36111111111</v>
+        <v>45663.35972222222</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>45677.45685047198</v>
+        <v>45679.43205396359</v>
       </c>
       <c r="D54" t="n">
-        <v>21737.86</v>
+        <v>23144.16</v>
       </c>
       <c r="E54" t="n">
-        <v>21711.54</v>
+        <v>22993.06</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-51</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45662.3625</v>
+        <v>45663.36111111111</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>45677.4611666516</v>
+        <v>45679.45217130476</v>
       </c>
       <c r="D55" t="n">
-        <v>21742.08</v>
+        <v>23171.13</v>
       </c>
       <c r="E55" t="n">
-        <v>21717.84</v>
+        <v>23158.49</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-52</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45662.36388888889</v>
+        <v>45663.3625</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>45677.4657679312</v>
+        <v>45679.47937049558</v>
       </c>
       <c r="D56" t="n">
-        <v>21746.71</v>
+        <v>23208.29</v>
       </c>
       <c r="E56" t="n">
-        <v>21719.51</v>
+        <v>23192.82</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-53</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45662.36527777778</v>
+        <v>45663.36388888889</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>45677.46909221537</v>
+        <v>45679.51430672187</v>
       </c>
       <c r="D57" t="n">
-        <v>21749.49</v>
+        <v>23256.6</v>
       </c>
       <c r="E57" t="n">
-        <v>21721.29</v>
+        <v>23241.11</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-54</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45662.36666666667</v>
+        <v>45663.36527777778</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>45678.29604698024</v>
+        <v>45680.40719872994</v>
       </c>
       <c r="D58" t="n">
-        <v>22938.31</v>
+        <v>24540.37</v>
       </c>
       <c r="E58" t="n">
-        <v>22909.59</v>
+        <v>24372.35</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-55</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45662.36944444444</v>
+        <v>45663.36666666667</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>45678.30023809815</v>
+        <v>45680.42812662325</v>
       </c>
       <c r="D59" t="n">
-        <v>22940.34</v>
+        <v>24568.5</v>
       </c>
       <c r="E59" t="n">
-        <v>22910.68</v>
+        <v>24554.18</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-56</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45662.37222222222</v>
+        <v>45663.36805555555</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>45678.30489852621</v>
+        <v>45680.45456403479</v>
       </c>
       <c r="D60" t="n">
-        <v>22943.05</v>
+        <v>24604.57</v>
       </c>
       <c r="E60" t="n">
-        <v>22915.49</v>
+        <v>24591.67</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-57</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45662.34583333333</v>
+        <v>45663.36944444444</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>45678.30506665447</v>
+        <v>45680.48123043847</v>
       </c>
       <c r="D61" t="n">
-        <v>22981.3</v>
+        <v>24640.97</v>
       </c>
       <c r="E61" t="n">
-        <v>21638.99</v>
+        <v>24628.03</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-58</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45662.37083333333</v>
+        <v>45663.37083333333</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>45678.30954380152</v>
+        <v>45680.50809453303</v>
       </c>
       <c r="D62" t="n">
-        <v>22951.74</v>
+        <v>24677.66</v>
       </c>
       <c r="E62" t="n">
-        <v>22924.32</v>
+        <v>24664.13</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-59</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45662.37638888889</v>
+        <v>45663.37222222222</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>45678.37065837454</v>
+        <v>45680.53992029219</v>
       </c>
       <c r="D63" t="n">
-        <v>23031.75</v>
+        <v>24721.49</v>
       </c>
       <c r="E63" t="n">
-        <v>23006.3</v>
+        <v>24706.53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-60</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45662.35416666666</v>
+        <v>45663.37361111111</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>45678.38042898908</v>
+        <v>45681.3109905868</v>
       </c>
       <c r="D64" t="n">
-        <v>23077.82</v>
+        <v>25829.83</v>
       </c>
       <c r="E64" t="n">
-        <v>22824.77</v>
+        <v>25814.99</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-61</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45662.35833333333</v>
+        <v>45663.375</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>45678.48975022274</v>
+        <v>45681.42196762541</v>
       </c>
       <c r="D65" t="n">
-        <v>23229.24</v>
+        <v>25987.63</v>
       </c>
       <c r="E65" t="n">
-        <v>22888.27</v>
+        <v>25869.35</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-62</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45662.36805555555</v>
+        <v>45663.37638888889</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>45679.30275021361</v>
+        <v>45681.440715653</v>
       </c>
       <c r="D66" t="n">
-        <v>24385.96</v>
+        <v>26012.63</v>
       </c>
       <c r="E66" t="n">
-        <v>23088.95</v>
+        <v>26000.21</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-63</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45662.375</v>
+        <v>45663.37777777778</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>45679.36613700811</v>
+        <v>45681.46127413044</v>
       </c>
       <c r="D67" t="n">
-        <v>24467.24</v>
+        <v>26040.23</v>
       </c>
       <c r="E67" t="n">
-        <v>24203.75</v>
+        <v>26029.14</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-64</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45662.37777777778</v>
+        <v>45663.37916666667</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>45679.45458931023</v>
+        <v>45681.48730194178</v>
       </c>
       <c r="D68" t="n">
-        <v>24590.61</v>
+        <v>26075.71</v>
       </c>
       <c r="E68" t="n">
-        <v>24563.46</v>
+        <v>26063.38</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-65</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>45662.37916666667</v>
+        <v>45663.38055555556</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>45679.45848119786</v>
+        <v>45681.51367038951</v>
       </c>
       <c r="D69" t="n">
-        <v>24594.21</v>
+        <v>26111.69</v>
       </c>
       <c r="E69" t="n">
-        <v>24564.99</v>
+        <v>26101.68</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-66</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>45662.37361111111</v>
+        <v>45663.38194444445</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>45679.46280503023</v>
+        <v>45681.53963501861</v>
       </c>
       <c r="D70" t="n">
-        <v>24608.44</v>
+        <v>26147.07</v>
       </c>
       <c r="E70" t="n">
-        <v>24302.1</v>
+        <v>26132.46</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-67</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>45662.38055555556</v>
+        <v>45663.38333333333</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>45679.46295694813</v>
+        <v>45684.31340396492</v>
       </c>
       <c r="D71" t="n">
-        <v>24598.66</v>
+        <v>30139.3</v>
       </c>
       <c r="E71" t="n">
-        <v>23490.82</v>
+        <v>30125.07</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-68</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45662.38194444445</v>
+        <v>45663.38472222222</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>45679.46685187928</v>
+        <v>45684.42820267653</v>
       </c>
       <c r="D72" t="n">
-        <v>24602.27</v>
+        <v>30302.61</v>
       </c>
       <c r="E72" t="n">
-        <v>23498.98</v>
+        <v>30183.28</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-69</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45662.38333333333</v>
+        <v>45663.38611111111</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>45679.47144544066</v>
+        <v>45684.44867335471</v>
       </c>
       <c r="D73" t="n">
-        <v>24606.88</v>
+        <v>30330.09</v>
       </c>
       <c r="E73" t="n">
-        <v>24577.72</v>
+        <v>30314.97</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-70</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45662.38611111111</v>
+        <v>45663.3875</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>45679.47506898885</v>
+        <v>45685.29747402589</v>
       </c>
       <c r="D74" t="n">
-        <v>24608.1</v>
+        <v>31550.36</v>
       </c>
       <c r="E74" t="n">
-        <v>24577.89</v>
+        <v>30363.88</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-71</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45662.3875</v>
+        <v>45663.38888888889</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>45679.47922680012</v>
+        <v>45685.42074876856</v>
       </c>
       <c r="D75" t="n">
-        <v>24612.09</v>
+        <v>31725.88</v>
       </c>
       <c r="E75" t="n">
-        <v>24585.72</v>
+        <v>31585.65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-72</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45662.38888888889</v>
+        <v>45663.39027777778</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>45679.48314812974</v>
+        <v>45685.4397684663</v>
       </c>
       <c r="D76" t="n">
-        <v>24615.73</v>
+        <v>31751.27</v>
       </c>
       <c r="E76" t="n">
-        <v>24588.25</v>
+        <v>31736.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-73</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>45662.39027777778</v>
+        <v>45663.39166666667</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>45679.48728703719</v>
+        <v>45685.46452595351</v>
       </c>
       <c r="D77" t="n">
-        <v>24619.69</v>
+        <v>31784.92</v>
       </c>
       <c r="E77" t="n">
-        <v>24593.78</v>
+        <v>31770.81</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-74</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>45662.39166666667</v>
+        <v>45663.39305555556</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>45679.49073334755</v>
+        <v>45685.49106106194</v>
       </c>
       <c r="D78" t="n">
-        <v>24622.66</v>
+        <v>31821.13</v>
       </c>
       <c r="E78" t="n">
-        <v>24601.31</v>
+        <v>31807.06</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-75</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>45662.39583333334</v>
+        <v>45663.39444444444</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>45680.29576971807</v>
+        <v>45685.51822108388</v>
       </c>
       <c r="D79" t="n">
-        <v>25775.91</v>
+        <v>31858.24</v>
       </c>
       <c r="E79" t="n">
-        <v>25749.21</v>
+        <v>31843.68</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-76</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>45662.4</v>
+        <v>45663.39583333334</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>45680.29836126349</v>
+        <v>45685.5391063725</v>
       </c>
       <c r="D80" t="n">
-        <v>25773.64</v>
+        <v>31886.31</v>
       </c>
       <c r="E80" t="n">
-        <v>25747.38</v>
+        <v>31875.13</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-77</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>45662.40138888889</v>
+        <v>45663.39722222222</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>45680.30192706605</v>
+        <v>45686.30411175941</v>
       </c>
       <c r="D81" t="n">
-        <v>25776.77</v>
+        <v>32985.92</v>
       </c>
       <c r="E81" t="n">
-        <v>25747.45</v>
+        <v>32974.68</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-78</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>45662.40416666667</v>
+        <v>45663.39861111111</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>45680.30552237033</v>
+        <v>45686.31916266631</v>
       </c>
       <c r="D82" t="n">
-        <v>25777.95</v>
+        <v>33005.59</v>
       </c>
       <c r="E82" t="n">
-        <v>25754.2</v>
+        <v>32991.52</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-79</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>45662.38472222222</v>
+        <v>45663.4</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>45680.30775151414</v>
+        <v>45686.43375581441</v>
       </c>
       <c r="D83" t="n">
-        <v>25809.16</v>
+        <v>33168.61</v>
       </c>
       <c r="E83" t="n">
-        <v>24537.75</v>
+        <v>33007.07</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-81</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45662.40694444445</v>
+        <v>45663.40277777778</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>45680.30977670962</v>
+        <v>45686.50867557069</v>
       </c>
       <c r="D84" t="n">
-        <v>25780.08</v>
+        <v>33272.49</v>
       </c>
       <c r="E84" t="n">
-        <v>25751.57</v>
+        <v>33259.78</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-82</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>45662.40833333333</v>
+        <v>45663.40416666667</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>45680.31349175517</v>
+        <v>45686.51292416641</v>
       </c>
       <c r="D85" t="n">
-        <v>25783.43</v>
+        <v>33276.61</v>
       </c>
       <c r="E85" t="n">
-        <v>25754.58</v>
+        <v>33261.12</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-80</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>45662.40972222222</v>
+        <v>45663.40138888889</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>45680.31586802262</v>
+        <v>45686.51377314926</v>
       </c>
       <c r="D86" t="n">
-        <v>25784.85</v>
+        <v>33281.83</v>
       </c>
       <c r="E86" t="n">
-        <v>25764.63</v>
+        <v>33160.59</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-83</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45662.41111111111</v>
+        <v>45663.40555555555</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>45680.3193618877</v>
+        <v>45686.51691270489</v>
       </c>
       <c r="D87" t="n">
-        <v>25787.88</v>
+        <v>33280.35</v>
       </c>
       <c r="E87" t="n">
-        <v>25761.42</v>
+        <v>33268.39</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-85</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45662.4125</v>
+        <v>45663.40833333333</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>45680.322826858</v>
+        <v>45687.29479495523</v>
       </c>
       <c r="D88" t="n">
-        <v>25790.87</v>
+        <v>34396.5</v>
       </c>
       <c r="E88" t="n">
-        <v>25762.06</v>
+        <v>34382.62</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-86</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45662.41388888889</v>
+        <v>45663.40972222222</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>45680.32727616818</v>
+        <v>45687.29866318146</v>
       </c>
       <c r="D89" t="n">
-        <v>25795.28</v>
+        <v>34400.07</v>
       </c>
       <c r="E89" t="n">
-        <v>25767.63</v>
+        <v>34385.9</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-84</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>45662.41527777778</v>
+        <v>45663.40694444445</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>45680.33194784635</v>
+        <v>45687.29938532144</v>
       </c>
       <c r="D90" t="n">
-        <v>25800</v>
+        <v>34405.11</v>
       </c>
       <c r="E90" t="n">
-        <v>25773.35</v>
+        <v>33280.45</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-87</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>45662.41666666666</v>
+        <v>45663.41111111111</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>45680.33647128829</v>
+        <v>45687.30274825758</v>
       </c>
       <c r="D91" t="n">
-        <v>25804.52</v>
+        <v>34403.96</v>
       </c>
       <c r="E91" t="n">
-        <v>25779.71</v>
+        <v>34391.38</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-88</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>45662.39444444444</v>
+        <v>45663.4125</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>45680.45165215246</v>
+        <v>45687.30631757227</v>
       </c>
       <c r="D92" t="n">
-        <v>26002.38</v>
+        <v>34407.1</v>
       </c>
       <c r="E92" t="n">
-        <v>25674.61</v>
+        <v>33317.69</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-89</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>45662.39305555556</v>
+        <v>45663.41388888889</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>45681.30395412225</v>
+        <v>45687.30961647203</v>
       </c>
       <c r="D93" t="n">
-        <v>27231.69</v>
+        <v>34409.85</v>
       </c>
       <c r="E93" t="n">
-        <v>25809.91</v>
+        <v>34397.41</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-90</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45662.41805555556</v>
+        <v>45663.41527777778</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>45681.4000094676</v>
+        <v>45687.31401063727</v>
       </c>
       <c r="D94" t="n">
-        <v>27334.01</v>
+        <v>34414.18</v>
       </c>
       <c r="E94" t="n">
-        <v>27305.33</v>
+        <v>34398.83</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-91</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45662.39722222222</v>
+        <v>45663.41666666666</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>45681.41150844435</v>
+        <v>45687.31862709111</v>
       </c>
       <c r="D95" t="n">
-        <v>27380.57</v>
+        <v>34418.82</v>
       </c>
       <c r="E95" t="n">
-        <v>27061.64</v>
+        <v>34402.86</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-92</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45662.39861111111</v>
+        <v>45663.41805555556</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>45681.5152986481</v>
+        <v>45687.38881641305</v>
       </c>
       <c r="D96" t="n">
-        <v>27528.03</v>
+        <v>34517.9</v>
       </c>
       <c r="E96" t="n">
-        <v>27220.58</v>
+        <v>34414.2</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-94</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45662.41944444444</v>
+        <v>45663.42083333333</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>45682.29557146539</v>
+        <v>45687.48434082514</v>
       </c>
       <c r="D97" t="n">
-        <v>28621.62</v>
+        <v>34651.45</v>
       </c>
       <c r="E97" t="n">
-        <v>28592.06</v>
+        <v>34639.36</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-93</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45662.40555555555</v>
+        <v>45663.41944444444</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>45682.30482944068</v>
+        <v>45687.48674930184</v>
       </c>
       <c r="D98" t="n">
-        <v>28654.95</v>
+        <v>34656.92</v>
       </c>
       <c r="E98" t="n">
-        <v>27387.42</v>
+        <v>34513.37</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-95</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45662.42083333333</v>
+        <v>45663.42222222222</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>45682.36125961172</v>
+        <v>45687.48880251114</v>
       </c>
       <c r="D99" t="n">
-        <v>28714.21</v>
+        <v>34655.88</v>
       </c>
       <c r="E99" t="n">
-        <v>28689.41</v>
+        <v>34641.11</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-96</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45662.42222222222</v>
+        <v>45663.42361111111</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>45682.36506481839</v>
+        <v>45687.49325692131</v>
       </c>
       <c r="D100" t="n">
-        <v>28717.69</v>
+        <v>34660.29</v>
       </c>
       <c r="E100" t="n">
-        <v>28688.22</v>
+        <v>34646.32</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-97</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45662.42361111111</v>
+        <v>45663.425</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>45682.36950473118</v>
+        <v>45687.49740479338</v>
       </c>
       <c r="D101" t="n">
-        <v>28722.09</v>
+        <v>34664.26</v>
       </c>
       <c r="E101" t="n">
-        <v>28690.55</v>
+        <v>34649.51</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-98</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45662.40277777778</v>
+        <v>45663.42638888889</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>45682.37171391879</v>
+        <v>45688.29722112227</v>
       </c>
       <c r="D102" t="n">
-        <v>28755.27</v>
+        <v>35814</v>
       </c>
       <c r="E102" t="n">
-        <v>28515.25</v>
+        <v>34663.57</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-100</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45662.425</v>
+        <v>45663.42916666667</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>45682.37232945213</v>
+        <v>45688.35846367258</v>
       </c>
       <c r="D103" t="n">
-        <v>28724.15</v>
+        <v>35898.19</v>
       </c>
       <c r="E103" t="n">
-        <v>28698.87</v>
+        <v>35884.8</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-99</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45662.42638888889</v>
+        <v>45663.42777777778</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>45682.37644474079</v>
+        <v>45688.36337761427</v>
       </c>
       <c r="D104" t="n">
-        <v>28728.08</v>
+        <v>35907.26</v>
       </c>
       <c r="E104" t="n">
-        <v>28700.18</v>
+        <v>35807.88</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-102</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45662.42777777778</v>
+        <v>45663.43194444444</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>45682.3806963802</v>
+        <v>45688.45307110677</v>
       </c>
       <c r="D105" t="n">
-        <v>28732.2</v>
+        <v>36030.42</v>
       </c>
       <c r="E105" t="n">
-        <v>28704.42</v>
+        <v>36015.54</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-101</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45662.42916666667</v>
+        <v>45663.43055555555</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>45682.38506751259</v>
+        <v>45688.45416635378</v>
       </c>
       <c r="D106" t="n">
-        <v>28736.5</v>
+        <v>36034</v>
       </c>
       <c r="E106" t="n">
-        <v>28709.36</v>
+        <v>35895.52</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-104</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45662.43055555555</v>
+        <v>45663.43472222222</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>45682.38970902534</v>
+        <v>45688.45672892279</v>
       </c>
       <c r="D107" t="n">
-        <v>28741.18</v>
+        <v>36031.69</v>
       </c>
       <c r="E107" t="n">
-        <v>28712.76</v>
+        <v>36019.86</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-105</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45662.43194444444</v>
+        <v>45663.43611111111</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>45682.39383160766</v>
+        <v>45688.46138404446</v>
       </c>
       <c r="D108" t="n">
-        <v>28745.12</v>
+        <v>36036.39</v>
       </c>
       <c r="E108" t="n">
-        <v>28715.49</v>
+        <v>36020.27</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-107</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45662.43333333333</v>
+        <v>45663.43888888889</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>45682.39839205483</v>
+        <v>45691.29459032765</v>
       </c>
       <c r="D109" t="n">
-        <v>28749.68</v>
+        <v>40112.21</v>
       </c>
       <c r="E109" t="n">
-        <v>28721.07</v>
+        <v>40098.89</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-106</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45662.43611111111</v>
+        <v>45663.4375</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>45682.40189128138</v>
+        <v>45691.29700716993</v>
       </c>
       <c r="D110" t="n">
-        <v>28750.72</v>
+        <v>40117.69</v>
       </c>
       <c r="E110" t="n">
-        <v>28722.48</v>
+        <v>36032.87</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-108</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45662.43472222222</v>
+        <v>45663.44027777778</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>45682.50878649591</v>
+        <v>45691.29916808461</v>
       </c>
       <c r="D111" t="n">
-        <v>28906.65</v>
+        <v>40116.8</v>
       </c>
       <c r="E111" t="n">
-        <v>27638.83</v>
+        <v>40102.64</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-109</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45662.44027777778</v>
+        <v>45663.44166666667</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>45683.29476731822</v>
+        <v>45691.30371936662</v>
       </c>
       <c r="D112" t="n">
-        <v>30030.46</v>
+        <v>40121.36</v>
       </c>
       <c r="E112" t="n">
-        <v>30006.79</v>
+        <v>40107.81</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-110</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45662.44305555556</v>
+        <v>45663.44305555556</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>45683.298002282</v>
+        <v>45691.30724517736</v>
       </c>
       <c r="D113" t="n">
-        <v>30031.12</v>
+        <v>40124.43</v>
       </c>
       <c r="E113" t="n">
-        <v>30004.98</v>
+        <v>40112.71</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Token-111</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45662.44444444445</v>
+        <v>45663.44444444445</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>45683.3022160192</v>
+        <v>45691.31132651552</v>
       </c>
       <c r="D114" t="n">
-        <v>30035.19</v>
+        <v>40128.31</v>
       </c>
       <c r="E114" t="n">
-        <v>30008.65</v>
+        <v>40113.93</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="n">
-        <v>45662.44583333333</v>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v>45683.30569821764</v>
-      </c>
-      <c r="D115" t="n">
-        <v>30038.21</v>
-      </c>
-      <c r="E115" t="n">
-        <v>30012.82</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="n">
-        <v>45662.4375</v>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v>45683.30742214988</v>
-      </c>
-      <c r="D116" t="n">
-        <v>30052.69</v>
-      </c>
-      <c r="E116" t="n">
-        <v>27785.09</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="n">
-        <v>45662.44861111111</v>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>45683.30945422715</v>
-      </c>
-      <c r="D117" t="n">
-        <v>30039.61</v>
-      </c>
-      <c r="E117" t="n">
-        <v>30014.03</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="n">
-        <v>45662.45277777778</v>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v>45683.31297951594</v>
-      </c>
-      <c r="D118" t="n">
-        <v>30038.69</v>
-      </c>
-      <c r="E118" t="n">
-        <v>30011.46</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="n">
-        <v>45662.45416666667</v>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v>45683.3914549181</v>
-      </c>
-      <c r="D119" t="n">
-        <v>30149.7</v>
-      </c>
-      <c r="E119" t="n">
-        <v>30121.08</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="n">
-        <v>45662.45555555556</v>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v>45683.39545692968</v>
-      </c>
-      <c r="D120" t="n">
-        <v>30153.46</v>
-      </c>
-      <c r="E120" t="n">
-        <v>30129.32</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="n">
-        <v>45662.44166666667</v>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v>45683.40281377276</v>
-      </c>
-      <c r="D121" t="n">
-        <v>30184.05</v>
-      </c>
-      <c r="E121" t="n">
-        <v>29954.72</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="n">
-        <v>45662.44722222222</v>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v>45683.48528964628</v>
-      </c>
-      <c r="D122" t="n">
-        <v>30294.82</v>
-      </c>
-      <c r="E122" t="n">
-        <v>30057.57</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="n">
-        <v>45662.43888888889</v>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>45683.53375720033</v>
-      </c>
-      <c r="D123" t="n">
-        <v>30376.61</v>
-      </c>
-      <c r="E123" t="n">
-        <v>29038.09</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="n">
-        <v>45662.45138888889</v>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>45684.30524191434</v>
-      </c>
-      <c r="D124" t="n">
-        <v>31469.55</v>
-      </c>
-      <c r="E124" t="n">
-        <v>30217.91</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="n">
-        <v>45662.45</v>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v>45684.40300360583</v>
-      </c>
-      <c r="D125" t="n">
-        <v>31612.33</v>
-      </c>
-      <c r="E125" t="n">
-        <v>31276.63</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Work with REO RPO to Correct (5.5.13.3) -&gt; Create Journal Entries? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Create/Post Journal Entries (5.5.13.4) -&gt; Unknown</t>
+          <t>Monthly -&gt; Monthly -&gt; Review AM using Asset Change Tracker (5.5.13.1) -&gt; Complete /Accurate? -&gt; Note Accuracy in Asset Change Tracker (5.5.13.2) -&gt; Unknown</t>
         </is>
       </c>
     </row>
@@ -4082,7 +3818,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -4092,7 +3828,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>96.77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -4102,7 +3838,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.36</v>
+        <v>22875.19</v>
       </c>
     </row>
     <row r="6">
@@ -4112,7 +3848,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.85</v>
+        <v>35881.35</v>
       </c>
     </row>
     <row r="7">
@@ -4122,7 +3858,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.46</v>
+        <v>22717.65</v>
       </c>
     </row>
   </sheetData>
